--- a/data_u1/data_2025-01-16_LSR3_H.xlsx
+++ b/data_u1/data_2025-01-16_LSR3_H.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EH36"/>
+  <dimension ref="A1:EM36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -582,465 +582,490 @@
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
+          <t>positive_baseline_n</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>positive_baseline</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>positive_mean</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>positive_sd</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>positive_change_endpoint</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>positive_completer</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>positive_sd_origin</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>negative_scale_name</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>negative_n</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>negative_baseline_n</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>negative_baseline</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>negative_mean</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>negative_sd</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>negative_change_endpoint</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>negative_completer</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>negative_sd_origin</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>functioning_scale_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>functioning_n</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>functioning_baseline</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>functioning_mean</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>functioning_sd</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>functioning_change_endpoint</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>functioning_completer</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>functioning_sd_origin</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>cognition_scale_name</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>cognition_n</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>cognition_baseline_n</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>cognition_baseline</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>cognition_mean</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>cognition_sd</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>cognition_change_endpoint</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>cognition_completer</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>cognition_sd_origin</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>depression_scale_name</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>depression_n</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>depression_baseline_n</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>depression_baseline</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>depression_mean</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>depression_sd</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>depression_change_endpoint</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>depression_completer</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>depression_sd_origin</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>weight_scale_name</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>weight_n</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>weight_baseline_n</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>weight_baseline</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>weight_mean</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>weight_sd</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>weight_change_endpoint</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>weight_completer</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>weight_sd_origin</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>Timepoint</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>prolactin_scale_name</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>prolactin_n</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>prolactin_baseline_n</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>prolactin_baseline</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>prolactin_mean</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>prolactin_sd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>prolactin_change_endpoint</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>prolactin_completer</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>prolactin_sd_origin</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>adverse_event_e</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>adverse_event_n</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>anticholinergic_symptom_e</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>anticholinergic_symptom_n</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>anxiety_e</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>anxiety_n</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>dizziness_e</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>dizziness_n</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>headache_e</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>headache_n</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>nausea_vomitting_e</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>nausea_vomitting_n</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>sedation_e</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>sedation_n</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>hyperprolactinemia_e</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>hyperprolactinemia_n</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>qtc_prolongation_e</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>qtc_prolongation_n</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>agitation_e</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>agitation_n</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>hypotension_e</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>hypotension_n</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>insomnia_e</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>insomnia_n</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>akathisia_e</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>akathisia_n</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>eps_symptoms_e</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>eps_symptoms_n</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>weight_increased_e</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>weight_increased_n</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>drug_new</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>timepoint</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>comparison_data</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>qtc_md_point</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>qtc_md_se</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>study_name_drug</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>crossover_periods</t>
         </is>
@@ -1235,115 +1260,121 @@
         <v>24</v>
       </c>
       <c r="AT2">
+        <v>24</v>
+      </c>
+      <c r="AU2">
         <v>13.1</v>
       </c>
-      <c r="AU2">
+      <c r="AV2">
         <v>-2.5</v>
       </c>
-      <c r="AV2">
+      <c r="AW2">
         <v>7.94</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>MMSE</t>
         </is>
       </c>
-      <c r="BQ2">
+      <c r="BS2">
         <v>23</v>
       </c>
-      <c r="BR2">
+      <c r="BT2">
+        <v>24</v>
+      </c>
+      <c r="BU2">
         <v>-25.1</v>
       </c>
-      <c r="BS2">
+      <c r="BV2">
         <v>0.8</v>
       </c>
-      <c r="BT2">
+      <c r="BW2">
         <v>2.2</v>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX2">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC2">
         <v>18</v>
       </c>
-      <c r="CY2">
+      <c r="DD2">
         <v>25</v>
       </c>
-      <c r="DD2">
+      <c r="DI2">
         <v>4</v>
       </c>
-      <c r="DE2">
+      <c r="DJ2">
         <v>25</v>
       </c>
-      <c r="DH2">
+      <c r="DM2">
         <v>3</v>
       </c>
-      <c r="DI2">
+      <c r="DN2">
         <v>25</v>
       </c>
-      <c r="DJ2">
+      <c r="DO2">
         <v>2</v>
       </c>
-      <c r="DK2">
+      <c r="DP2">
         <v>25</v>
       </c>
-      <c r="DR2">
+      <c r="DW2">
         <v>13</v>
       </c>
-      <c r="DS2">
+      <c r="DX2">
         <v>25</v>
       </c>
-      <c r="DT2">
+      <c r="DY2">
         <v>2</v>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>Isaacson (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH2">
+      <c r="EM2">
         <v>1</v>
       </c>
     </row>
@@ -1536,130 +1567,136 @@
         <v>14</v>
       </c>
       <c r="AT3">
+        <v>14</v>
+      </c>
+      <c r="AU3">
         <v>14.7</v>
       </c>
-      <c r="AU3">
+      <c r="AV3">
         <v>-1.4</v>
       </c>
-      <c r="AV3">
+      <c r="AW3">
         <v>7.71</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>MMSE</t>
         </is>
       </c>
-      <c r="BQ3">
+      <c r="BS3">
         <v>14</v>
       </c>
-      <c r="BR3">
+      <c r="BT3">
+        <v>14</v>
+      </c>
+      <c r="BU3">
         <v>-24.7</v>
       </c>
-      <c r="BS3">
+      <c r="BV3">
         <v>-0.3</v>
       </c>
-      <c r="BT3">
+      <c r="BW3">
         <v>1.99</v>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX3">
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC3">
         <v>12</v>
       </c>
-      <c r="CY3">
+      <c r="DD3">
         <v>14</v>
       </c>
-      <c r="DB3">
+      <c r="DG3">
         <v>0</v>
       </c>
-      <c r="DC3">
+      <c r="DH3">
         <v>14</v>
       </c>
-      <c r="DD3">
+      <c r="DI3">
         <v>1</v>
       </c>
-      <c r="DE3">
+      <c r="DJ3">
         <v>14</v>
       </c>
-      <c r="DH3">
+      <c r="DM3">
         <v>1</v>
       </c>
-      <c r="DI3">
+      <c r="DN3">
         <v>14</v>
       </c>
-      <c r="DJ3">
+      <c r="DO3">
         <v>2</v>
       </c>
-      <c r="DK3">
+      <c r="DP3">
         <v>14</v>
       </c>
-      <c r="DP3">
+      <c r="DU3">
         <v>1</v>
       </c>
-      <c r="DQ3">
+      <c r="DV3">
         <v>14</v>
       </c>
-      <c r="DR3">
+      <c r="DW3">
         <v>11</v>
       </c>
-      <c r="DS3">
+      <c r="DX3">
         <v>14</v>
       </c>
-      <c r="DT3">
+      <c r="DY3">
         <v>1</v>
       </c>
-      <c r="DU3">
+      <c r="DZ3">
         <v>14</v>
       </c>
-      <c r="EB3" t="inlineStr">
+      <c r="EG3" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC3" t="inlineStr">
+      <c r="EH3" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
         <is>
           <t>Isaacson (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH3">
+      <c r="EM3">
         <v>1</v>
       </c>
     </row>
@@ -1858,249 +1895,258 @@
         <v>120</v>
       </c>
       <c r="AT4">
+        <v>120</v>
+      </c>
+      <c r="AU4">
         <v>25.8</v>
       </c>
-      <c r="AU4">
+      <c r="AV4">
         <v>-5.5</v>
       </c>
-      <c r="AV4">
+      <c r="AW4">
         <v>5.48</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
           <t>BNSS total</t>
         </is>
       </c>
-      <c r="BA4">
+      <c r="BB4">
         <v>120</v>
       </c>
-      <c r="BB4">
+      <c r="BC4">
+        <v>120</v>
+      </c>
+      <c r="BD4">
         <v>37.2</v>
       </c>
-      <c r="BC4">
+      <c r="BE4">
         <v>-7.1</v>
       </c>
-      <c r="BD4">
+      <c r="BF4">
         <v>10.95</v>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
         <is>
           <t>MADRS</t>
         </is>
       </c>
-      <c r="BY4">
+      <c r="CB4">
         <v>120</v>
       </c>
-      <c r="BZ4">
+      <c r="CC4">
         <v>120</v>
       </c>
-      <c r="CA4">
+      <c r="CD4">
         <v>13.1</v>
       </c>
-      <c r="CB4">
+      <c r="CE4">
         <v>-3.3</v>
       </c>
-      <c r="CC4">
+      <c r="CF4">
         <v>6.57</v>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>weight kg</t>
         </is>
       </c>
-      <c r="CH4">
+      <c r="CK4">
         <v>120</v>
       </c>
-      <c r="CI4">
+      <c r="CL4">
+        <v>120</v>
+      </c>
+      <c r="CM4">
         <v>75.40000000000001</v>
       </c>
-      <c r="CJ4">
+      <c r="CN4">
         <v>0.3</v>
       </c>
-      <c r="CK4">
+      <c r="CO4">
         <v>1.9</v>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
         <is>
           <t>4 weeks</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>prolactin levels ng/ml</t>
         </is>
       </c>
-      <c r="CQ4">
+      <c r="CU4">
         <v>114</v>
       </c>
-      <c r="CS4">
+      <c r="CX4">
         <v>-1.965789473684211</v>
       </c>
-      <c r="CT4">
+      <c r="CY4">
         <v>28</v>
       </c>
-      <c r="CU4" t="inlineStr">
+      <c r="CZ4" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CW4" t="inlineStr">
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CX4">
+      <c r="DC4">
         <v>55</v>
       </c>
-      <c r="CY4">
+      <c r="DD4">
         <v>120</v>
       </c>
-      <c r="DB4">
+      <c r="DG4">
         <v>2</v>
       </c>
-      <c r="DC4">
+      <c r="DH4">
         <v>120</v>
       </c>
-      <c r="DF4">
+      <c r="DK4">
         <v>11</v>
       </c>
-      <c r="DG4">
+      <c r="DL4">
         <v>120</v>
       </c>
-      <c r="DH4">
+      <c r="DM4">
         <v>6</v>
       </c>
-      <c r="DI4">
+      <c r="DN4">
         <v>120</v>
       </c>
-      <c r="DJ4">
+      <c r="DO4">
         <v>8</v>
       </c>
-      <c r="DK4">
+      <c r="DP4">
         <v>120</v>
       </c>
-      <c r="DN4">
+      <c r="DS4">
         <v>0</v>
       </c>
-      <c r="DO4">
+      <c r="DT4">
         <v>120</v>
       </c>
-      <c r="DP4">
+      <c r="DU4">
         <v>6</v>
       </c>
-      <c r="DQ4">
+      <c r="DV4">
         <v>120</v>
       </c>
-      <c r="DT4">
+      <c r="DY4">
         <v>4</v>
       </c>
-      <c r="DU4">
+      <c r="DZ4">
         <v>120</v>
       </c>
-      <c r="DV4">
+      <c r="EA4">
         <v>1</v>
       </c>
-      <c r="DW4">
+      <c r="EB4">
         <v>120</v>
       </c>
-      <c r="DX4">
+      <c r="EC4">
         <v>4</v>
       </c>
-      <c r="DY4">
+      <c r="ED4">
         <v>120</v>
       </c>
-      <c r="DZ4">
+      <c r="EE4">
         <v>1</v>
       </c>
-      <c r="EA4">
+      <c r="EF4">
         <v>120</v>
       </c>
-      <c r="EB4" t="inlineStr">
+      <c r="EG4" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC4" t="inlineStr">
+      <c r="EH4" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
         <is>
           <t>Koblan (2020) - ulotaront</t>
         </is>
       </c>
-      <c r="EH4">
+      <c r="EM4">
         <v>1</v>
       </c>
     </row>
@@ -2299,249 +2345,258 @@
         <v>125</v>
       </c>
       <c r="AT5">
+        <v>125</v>
+      </c>
+      <c r="AU5">
         <v>25.4</v>
       </c>
-      <c r="AU5">
+      <c r="AV5">
         <v>-3.9</v>
       </c>
-      <c r="AV5">
+      <c r="AW5">
         <v>5.59</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
           <t>BNSS total</t>
         </is>
       </c>
-      <c r="BA5">
+      <c r="BB5">
         <v>125</v>
       </c>
-      <c r="BB5">
+      <c r="BC5">
+        <v>125</v>
+      </c>
+      <c r="BD5">
         <v>37.4</v>
       </c>
-      <c r="BC5">
+      <c r="BE5">
         <v>-2.7</v>
       </c>
-      <c r="BD5">
+      <c r="BF5">
         <v>10.06</v>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
         <is>
           <t>MADRS</t>
         </is>
       </c>
-      <c r="BY5">
+      <c r="CB5">
         <v>125</v>
       </c>
-      <c r="BZ5">
+      <c r="CC5">
         <v>125</v>
       </c>
-      <c r="CA5">
+      <c r="CD5">
         <v>12.6</v>
       </c>
-      <c r="CB5">
+      <c r="CE5">
         <v>-1.6</v>
       </c>
-      <c r="CC5">
+      <c r="CF5">
         <v>6.71</v>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>weight kg</t>
         </is>
       </c>
-      <c r="CH5">
+      <c r="CK5">
         <v>125</v>
       </c>
-      <c r="CI5">
+      <c r="CL5">
+        <v>125</v>
+      </c>
+      <c r="CM5">
         <v>75.40000000000001</v>
       </c>
-      <c r="CJ5">
+      <c r="CN5">
         <v>-0.1</v>
       </c>
-      <c r="CK5">
+      <c r="CO5">
         <v>2.3</v>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
         <is>
           <t>4 weeks</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>prolactin levels ng/ml</t>
         </is>
       </c>
-      <c r="CQ5">
+      <c r="CU5">
         <v>113</v>
       </c>
-      <c r="CS5">
+      <c r="CX5">
         <v>-1.383805309734513</v>
       </c>
-      <c r="CT5">
+      <c r="CY5">
         <v>28</v>
       </c>
-      <c r="CU5" t="inlineStr">
+      <c r="CZ5" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CW5" t="inlineStr">
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CX5">
+      <c r="DC5">
         <v>63</v>
       </c>
-      <c r="CY5">
+      <c r="DD5">
         <v>125</v>
       </c>
-      <c r="DB5">
+      <c r="DG5">
         <v>9</v>
       </c>
-      <c r="DC5">
+      <c r="DH5">
         <v>125</v>
       </c>
-      <c r="DF5">
+      <c r="DK5">
         <v>15</v>
       </c>
-      <c r="DG5">
+      <c r="DL5">
         <v>125</v>
       </c>
-      <c r="DH5">
+      <c r="DM5">
         <v>4</v>
       </c>
-      <c r="DI5">
+      <c r="DN5">
         <v>125</v>
       </c>
-      <c r="DJ5">
+      <c r="DO5">
         <v>6</v>
       </c>
-      <c r="DK5">
+      <c r="DP5">
         <v>125</v>
       </c>
-      <c r="DN5">
+      <c r="DS5">
         <v>0</v>
       </c>
-      <c r="DO5">
+      <c r="DT5">
         <v>125</v>
       </c>
-      <c r="DP5">
+      <c r="DU5">
         <v>6</v>
       </c>
-      <c r="DQ5">
+      <c r="DV5">
         <v>125</v>
       </c>
-      <c r="DT5">
+      <c r="DY5">
         <v>13</v>
       </c>
-      <c r="DU5">
+      <c r="DZ5">
         <v>125</v>
       </c>
-      <c r="DV5">
+      <c r="EA5">
         <v>0</v>
       </c>
-      <c r="DW5">
+      <c r="EB5">
         <v>125</v>
       </c>
-      <c r="DX5">
+      <c r="EC5">
         <v>4</v>
       </c>
-      <c r="DY5">
+      <c r="ED5">
         <v>125</v>
       </c>
-      <c r="DZ5">
+      <c r="EE5">
         <v>1</v>
       </c>
-      <c r="EA5">
+      <c r="EF5">
         <v>125</v>
       </c>
-      <c r="EB5" t="inlineStr">
+      <c r="EG5" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC5" t="inlineStr">
+      <c r="EH5" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG5" t="inlineStr">
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
         <is>
           <t>Koblan (2020) - ulotaront</t>
         </is>
       </c>
-      <c r="EH5">
+      <c r="EM5">
         <v>1</v>
       </c>
     </row>
@@ -2693,27 +2748,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB6" t="inlineStr">
+      <c r="EG6" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC6" t="inlineStr">
+      <c r="EH6" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG6" t="inlineStr">
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH6">
+      <c r="EM6">
         <v>1</v>
       </c>
     </row>
@@ -2865,27 +2920,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB7" t="inlineStr">
+      <c r="EG7" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC7" t="inlineStr">
+      <c r="EH7" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG7" t="inlineStr">
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH7">
+      <c r="EM7">
         <v>1</v>
       </c>
     </row>
@@ -3037,27 +3092,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB8" t="inlineStr">
+      <c r="EG8" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC8" t="inlineStr">
+      <c r="EH8" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG8" t="inlineStr">
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH8">
+      <c r="EM8">
         <v>1</v>
       </c>
     </row>
@@ -3209,27 +3264,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB9" t="inlineStr">
+      <c r="EG9" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC9" t="inlineStr">
+      <c r="EH9" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG9" t="inlineStr">
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH9">
+      <c r="EM9">
         <v>1</v>
       </c>
     </row>
@@ -3381,27 +3436,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB10" t="inlineStr">
+      <c r="EG10" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC10" t="inlineStr">
+      <c r="EH10" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG10" t="inlineStr">
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH10">
+      <c r="EM10">
         <v>1</v>
       </c>
     </row>
@@ -3553,27 +3608,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="EB11" t="inlineStr">
+      <c r="EG11" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC11" t="inlineStr">
+      <c r="EH11" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG11" t="inlineStr">
+      <c r="EI11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL11" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH11">
+      <c r="EM11">
         <v>1</v>
       </c>
     </row>
@@ -3767,24 +3822,22 @@
         <v>54</v>
       </c>
       <c r="AT12">
+        <v>72</v>
+      </c>
+      <c r="AU12">
         <v>26.86</v>
       </c>
-      <c r="AU12">
+      <c r="AV12">
         <v>23.61</v>
       </c>
-      <c r="AV12">
+      <c r="AW12">
         <v>6.64</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3792,134 +3845,142 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA12">
+      <c r="BB12">
         <v>54</v>
       </c>
-      <c r="BB12">
+      <c r="BC12">
+        <v>72</v>
+      </c>
+      <c r="BD12">
         <v>24.1</v>
       </c>
-      <c r="BC12">
+      <c r="BE12">
         <v>22.65</v>
       </c>
-      <c r="BD12">
+      <c r="BF12">
         <v>5.81</v>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BY12">
+      <c r="CB12">
         <v>54</v>
       </c>
-      <c r="BZ12">
+      <c r="CC12">
         <v>72</v>
       </c>
-      <c r="CA12">
+      <c r="CD12">
         <v>11.58</v>
       </c>
-      <c r="CB12">
+      <c r="CE12">
         <v>9.56</v>
       </c>
-      <c r="CC12">
+      <c r="CF12">
         <v>4.03</v>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX12">
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC12">
         <v>23</v>
       </c>
-      <c r="CY12">
+      <c r="DD12">
         <v>72</v>
       </c>
-      <c r="DB12">
+      <c r="DG12">
         <v>6</v>
       </c>
-      <c r="DC12">
+      <c r="DH12">
         <v>72</v>
       </c>
-      <c r="DF12">
+      <c r="DK12">
         <v>4</v>
       </c>
-      <c r="DG12">
+      <c r="DL12">
         <v>72</v>
       </c>
-      <c r="DH12">
+      <c r="DM12">
         <v>4</v>
       </c>
-      <c r="DI12">
+      <c r="DN12">
         <v>72</v>
       </c>
-      <c r="DP12">
+      <c r="DU12">
         <v>2</v>
       </c>
-      <c r="DQ12">
+      <c r="DV12">
         <v>72</v>
       </c>
-      <c r="DT12">
+      <c r="DY12">
         <v>1</v>
       </c>
-      <c r="DU12">
+      <c r="DZ12">
         <v>72</v>
       </c>
-      <c r="DZ12">
+      <c r="EE12">
         <v>1</v>
       </c>
-      <c r="EA12">
+      <c r="EF12">
         <v>72</v>
       </c>
-      <c r="EB12" t="inlineStr">
+      <c r="EG12" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC12" t="inlineStr">
+      <c r="EH12" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG12" t="inlineStr">
+      <c r="EI12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL12" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH12">
+      <c r="EM12">
         <v>1</v>
       </c>
     </row>
@@ -4113,24 +4174,22 @@
         <v>49</v>
       </c>
       <c r="AT13">
+        <v>65</v>
+      </c>
+      <c r="AU13">
         <v>26.2</v>
       </c>
-      <c r="AU13">
+      <c r="AV13">
         <v>23.41</v>
       </c>
-      <c r="AV13">
+      <c r="AW13">
         <v>6.14</v>
       </c>
-      <c r="AW13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4138,134 +4197,142 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA13">
+      <c r="BB13">
         <v>49</v>
       </c>
-      <c r="BB13">
+      <c r="BC13">
+        <v>65</v>
+      </c>
+      <c r="BD13">
         <v>23.65</v>
       </c>
-      <c r="BC13">
+      <c r="BE13">
         <v>21.82</v>
       </c>
-      <c r="BD13">
+      <c r="BF13">
         <v>5.85</v>
       </c>
-      <c r="BE13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BY13">
+      <c r="CB13">
         <v>49</v>
       </c>
-      <c r="BZ13">
+      <c r="CC13">
         <v>65</v>
       </c>
-      <c r="CA13">
+      <c r="CD13">
         <v>12.91</v>
       </c>
-      <c r="CB13">
+      <c r="CE13">
         <v>9.880000000000001</v>
       </c>
-      <c r="CC13">
+      <c r="CF13">
         <v>4.15</v>
       </c>
-      <c r="CD13" t="inlineStr">
+      <c r="CG13" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX13">
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC13">
         <v>14</v>
       </c>
-      <c r="CY13">
+      <c r="DD13">
         <v>65</v>
       </c>
-      <c r="DB13">
+      <c r="DG13">
         <v>3</v>
       </c>
-      <c r="DC13">
+      <c r="DH13">
         <v>65</v>
       </c>
-      <c r="DF13">
+      <c r="DK13">
         <v>4</v>
       </c>
-      <c r="DG13">
+      <c r="DL13">
         <v>65</v>
       </c>
-      <c r="DH13">
+      <c r="DM13">
         <v>0</v>
       </c>
-      <c r="DI13">
+      <c r="DN13">
         <v>65</v>
       </c>
-      <c r="DP13">
+      <c r="DU13">
         <v>0</v>
       </c>
-      <c r="DQ13">
+      <c r="DV13">
         <v>65</v>
       </c>
-      <c r="DT13">
+      <c r="DY13">
         <v>3</v>
       </c>
-      <c r="DU13">
+      <c r="DZ13">
         <v>65</v>
       </c>
-      <c r="DZ13">
+      <c r="EE13">
         <v>2</v>
       </c>
-      <c r="EA13">
+      <c r="EF13">
         <v>65</v>
       </c>
-      <c r="EB13" t="inlineStr">
+      <c r="EG13" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC13" t="inlineStr">
+      <c r="EH13" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG13" t="inlineStr">
+      <c r="EI13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL13" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH13">
+      <c r="EM13">
         <v>1</v>
       </c>
     </row>
@@ -4459,24 +4526,22 @@
         <v>51</v>
       </c>
       <c r="AT14">
+        <v>68</v>
+      </c>
+      <c r="AU14">
         <v>27.26</v>
       </c>
-      <c r="AU14">
+      <c r="AV14">
         <v>22.22</v>
       </c>
-      <c r="AV14">
+      <c r="AW14">
         <v>6.5</v>
       </c>
-      <c r="AW14" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4484,134 +4549,142 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA14">
+      <c r="BB14">
         <v>51</v>
       </c>
-      <c r="BB14">
+      <c r="BC14">
+        <v>68</v>
+      </c>
+      <c r="BD14">
         <v>24.59</v>
       </c>
-      <c r="BC14">
+      <c r="BE14">
         <v>22.53</v>
       </c>
-      <c r="BD14">
+      <c r="BF14">
         <v>5.41</v>
       </c>
-      <c r="BE14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BY14">
+      <c r="CB14">
         <v>51</v>
       </c>
-      <c r="BZ14">
+      <c r="CC14">
         <v>68</v>
       </c>
-      <c r="CA14">
+      <c r="CD14">
         <v>11.54</v>
       </c>
-      <c r="CB14">
+      <c r="CE14">
         <v>9.06</v>
       </c>
-      <c r="CC14">
+      <c r="CF14">
         <v>4.08</v>
       </c>
-      <c r="CD14" t="inlineStr">
+      <c r="CG14" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX14">
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC14">
         <v>23</v>
       </c>
-      <c r="CY14">
+      <c r="DD14">
         <v>68</v>
       </c>
-      <c r="DB14">
+      <c r="DG14">
         <v>2</v>
       </c>
-      <c r="DC14">
+      <c r="DH14">
         <v>68</v>
       </c>
-      <c r="DF14">
+      <c r="DK14">
         <v>5</v>
       </c>
-      <c r="DG14">
+      <c r="DL14">
         <v>68</v>
       </c>
-      <c r="DH14">
+      <c r="DM14">
         <v>2</v>
       </c>
-      <c r="DI14">
+      <c r="DN14">
         <v>68</v>
       </c>
-      <c r="DP14">
+      <c r="DU14">
         <v>8</v>
       </c>
-      <c r="DQ14">
+      <c r="DV14">
         <v>68</v>
       </c>
-      <c r="DT14">
+      <c r="DY14">
         <v>5</v>
       </c>
-      <c r="DU14">
+      <c r="DZ14">
         <v>68</v>
       </c>
-      <c r="DZ14">
+      <c r="EE14">
         <v>0</v>
       </c>
-      <c r="EA14">
+      <c r="EF14">
         <v>68</v>
       </c>
-      <c r="EB14" t="inlineStr">
+      <c r="EG14" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC14" t="inlineStr">
+      <c r="EH14" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
+      <c r="EI14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH14">
+      <c r="EM14">
         <v>1</v>
       </c>
     </row>
@@ -4805,24 +4878,22 @@
         <v>56</v>
       </c>
       <c r="AT15">
+        <v>71</v>
+      </c>
+      <c r="AU15">
         <v>27.49</v>
       </c>
-      <c r="AU15">
+      <c r="AV15">
         <v>19.52</v>
       </c>
-      <c r="AV15">
+      <c r="AW15">
         <v>5.11</v>
       </c>
-      <c r="AW15" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4830,134 +4901,142 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
           <t>PANSS negative</t>
         </is>
       </c>
-      <c r="BA15">
+      <c r="BB15">
         <v>56</v>
       </c>
-      <c r="BB15">
+      <c r="BC15">
+        <v>71</v>
+      </c>
+      <c r="BD15">
         <v>23.65</v>
       </c>
-      <c r="BC15">
+      <c r="BE15">
         <v>21.45</v>
       </c>
-      <c r="BD15">
+      <c r="BF15">
         <v>5.13</v>
       </c>
-      <c r="BE15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
         <is>
           <t>PANSS anxiety/depression</t>
         </is>
       </c>
-      <c r="BY15">
+      <c r="CB15">
         <v>56</v>
       </c>
-      <c r="BZ15">
+      <c r="CC15">
         <v>71</v>
       </c>
-      <c r="CA15">
+      <c r="CD15">
         <v>12.58</v>
       </c>
-      <c r="CB15">
+      <c r="CE15">
         <v>8.5</v>
       </c>
-      <c r="CC15">
+      <c r="CF15">
         <v>4.09</v>
       </c>
-      <c r="CD15" t="inlineStr">
+      <c r="CG15" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX15">
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC15">
         <v>36</v>
       </c>
-      <c r="CY15">
+      <c r="DD15">
         <v>71</v>
       </c>
-      <c r="DB15">
+      <c r="DG15">
         <v>5</v>
       </c>
-      <c r="DC15">
+      <c r="DH15">
         <v>71</v>
       </c>
-      <c r="DF15">
+      <c r="DK15">
         <v>6</v>
       </c>
-      <c r="DG15">
+      <c r="DL15">
         <v>71</v>
       </c>
-      <c r="DH15">
+      <c r="DM15">
         <v>6</v>
       </c>
-      <c r="DI15">
+      <c r="DN15">
         <v>71</v>
       </c>
-      <c r="DP15">
+      <c r="DU15">
         <v>0</v>
       </c>
-      <c r="DQ15">
+      <c r="DV15">
         <v>71</v>
       </c>
-      <c r="DT15">
+      <c r="DY15">
         <v>5</v>
       </c>
-      <c r="DU15">
+      <c r="DZ15">
         <v>71</v>
       </c>
-      <c r="DZ15">
+      <c r="EE15">
         <v>8</v>
       </c>
-      <c r="EA15">
+      <c r="EF15">
         <v>71</v>
       </c>
-      <c r="EB15" t="inlineStr">
+      <c r="EG15" t="inlineStr">
         <is>
           <t>D2 antipsychotic</t>
         </is>
       </c>
-      <c r="EC15" t="inlineStr">
+      <c r="EH15" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG15" t="inlineStr">
+      <c r="EI15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL15" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH15">
+      <c r="EM15">
         <v>1</v>
       </c>
     </row>
@@ -5067,69 +5146,69 @@
           <t>34</t>
         </is>
       </c>
-      <c r="CX16">
+      <c r="DC16">
         <v>16</v>
       </c>
-      <c r="CY16">
+      <c r="DD16">
         <v>34</v>
       </c>
-      <c r="CZ16">
+      <c r="DE16">
         <v>0</v>
       </c>
-      <c r="DA16">
+      <c r="DF16">
         <v>34</v>
       </c>
-      <c r="DB16">
+      <c r="DG16">
         <v>0</v>
       </c>
-      <c r="DC16">
+      <c r="DH16">
         <v>34</v>
       </c>
-      <c r="DD16">
+      <c r="DI16">
         <v>2</v>
       </c>
-      <c r="DE16">
+      <c r="DJ16">
         <v>34</v>
       </c>
-      <c r="DF16">
+      <c r="DK16">
         <v>7</v>
       </c>
-      <c r="DG16">
+      <c r="DL16">
         <v>34</v>
       </c>
-      <c r="DH16">
+      <c r="DM16">
         <v>0</v>
       </c>
-      <c r="DI16">
+      <c r="DN16">
         <v>34</v>
       </c>
-      <c r="DJ16">
+      <c r="DO16">
         <v>5</v>
       </c>
-      <c r="DK16">
+      <c r="DP16">
         <v>34</v>
       </c>
-      <c r="EB16" t="inlineStr">
+      <c r="EG16" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC16" t="inlineStr">
+      <c r="EH16" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
+      <c r="EI16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL16" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH16">
+      <c r="EM16">
         <v>1</v>
       </c>
     </row>
@@ -5239,69 +5318,69 @@
           <t>35</t>
         </is>
       </c>
-      <c r="CX17">
+      <c r="DC17">
         <v>34</v>
       </c>
-      <c r="CY17">
+      <c r="DD17">
         <v>35</v>
       </c>
-      <c r="CZ17">
+      <c r="DE17">
         <v>5</v>
       </c>
-      <c r="DA17">
+      <c r="DF17">
         <v>35</v>
       </c>
-      <c r="DB17">
+      <c r="DG17">
         <v>0</v>
       </c>
-      <c r="DC17">
+      <c r="DH17">
         <v>35</v>
       </c>
-      <c r="DD17">
+      <c r="DI17">
         <v>10</v>
       </c>
-      <c r="DE17">
+      <c r="DJ17">
         <v>35</v>
       </c>
-      <c r="DF17">
+      <c r="DK17">
         <v>4</v>
       </c>
-      <c r="DG17">
+      <c r="DL17">
         <v>35</v>
       </c>
-      <c r="DH17">
+      <c r="DM17">
         <v>12</v>
       </c>
-      <c r="DI17">
+      <c r="DN17">
         <v>35</v>
       </c>
-      <c r="DJ17">
+      <c r="DO17">
         <v>21</v>
       </c>
-      <c r="DK17">
+      <c r="DP17">
         <v>35</v>
       </c>
-      <c r="EB17" t="inlineStr">
+      <c r="EG17" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC17" t="inlineStr">
+      <c r="EH17" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr">
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL17" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH17">
+      <c r="EM17">
         <v>1</v>
       </c>
     </row>
@@ -5411,69 +5490,69 @@
           <t>36</t>
         </is>
       </c>
-      <c r="CX18">
+      <c r="DC18">
         <v>15</v>
       </c>
-      <c r="CY18">
+      <c r="DD18">
         <v>36</v>
       </c>
-      <c r="CZ18">
+      <c r="DE18">
         <v>0</v>
       </c>
-      <c r="DA18">
+      <c r="DF18">
         <v>36</v>
       </c>
-      <c r="DB18">
+      <c r="DG18">
         <v>3</v>
       </c>
-      <c r="DC18">
+      <c r="DH18">
         <v>36</v>
       </c>
-      <c r="DD18">
+      <c r="DI18">
         <v>1</v>
       </c>
-      <c r="DE18">
+      <c r="DJ18">
         <v>36</v>
       </c>
-      <c r="DF18">
+      <c r="DK18">
         <v>1</v>
       </c>
-      <c r="DG18">
+      <c r="DL18">
         <v>36</v>
       </c>
-      <c r="DH18">
+      <c r="DM18">
         <v>0</v>
       </c>
-      <c r="DI18">
+      <c r="DN18">
         <v>36</v>
       </c>
-      <c r="DJ18">
+      <c r="DO18">
         <v>5</v>
       </c>
-      <c r="DK18">
+      <c r="DP18">
         <v>36</v>
       </c>
-      <c r="EB18" t="inlineStr">
+      <c r="EG18" t="inlineStr">
         <is>
           <t>D2 antipsychotic</t>
         </is>
       </c>
-      <c r="EC18" t="inlineStr">
+      <c r="EH18" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG18" t="inlineStr">
+      <c r="EI18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL18" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH18">
+      <c r="EM18">
         <v>1</v>
       </c>
     </row>
@@ -5578,63 +5657,63 @@
           <t>63</t>
         </is>
       </c>
-      <c r="CX19">
+      <c r="DC19">
         <v>2</v>
       </c>
-      <c r="CY19">
+      <c r="DD19">
         <v>63</v>
       </c>
-      <c r="DD19">
+      <c r="DI19">
         <v>1</v>
       </c>
-      <c r="DE19">
+      <c r="DJ19">
         <v>63</v>
       </c>
-      <c r="DH19">
+      <c r="DM19">
         <v>1</v>
       </c>
-      <c r="DI19">
+      <c r="DN19">
         <v>63</v>
       </c>
-      <c r="DJ19">
+      <c r="DO19">
         <v>0</v>
       </c>
-      <c r="DK19">
+      <c r="DP19">
         <v>63</v>
       </c>
-      <c r="DN19">
+      <c r="DS19">
         <v>1</v>
       </c>
-      <c r="DO19">
+      <c r="DT19">
         <v>59</v>
       </c>
-      <c r="EB19" t="inlineStr">
+      <c r="EG19" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC19" t="inlineStr">
+      <c r="EH19" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EE19">
+      <c r="EI19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EJ19">
         <v>1.248958333333333</v>
       </c>
-      <c r="EF19">
+      <c r="EK19">
         <v>2.100625000000001</v>
       </c>
-      <c r="EG19" t="inlineStr">
+      <c r="EL19" t="inlineStr">
         <is>
           <t>Tsukada (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH19">
+      <c r="EM19">
         <v>2</v>
       </c>
     </row>
@@ -5749,63 +5828,63 @@
           <t>63</t>
         </is>
       </c>
-      <c r="CX20">
+      <c r="DC20">
         <v>32</v>
       </c>
-      <c r="CY20">
+      <c r="DD20">
         <v>63</v>
       </c>
-      <c r="DD20">
+      <c r="DI20">
         <v>7</v>
       </c>
-      <c r="DE20">
+      <c r="DJ20">
         <v>63</v>
       </c>
-      <c r="DH20">
+      <c r="DM20">
         <v>16</v>
       </c>
-      <c r="DI20">
+      <c r="DN20">
         <v>63</v>
       </c>
-      <c r="DJ20">
+      <c r="DO20">
         <v>16</v>
       </c>
-      <c r="DK20">
+      <c r="DP20">
         <v>63</v>
       </c>
-      <c r="DN20">
+      <c r="DS20">
         <v>5</v>
       </c>
-      <c r="DO20">
+      <c r="DT20">
         <v>62</v>
       </c>
-      <c r="EB20" t="inlineStr">
+      <c r="EG20" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC20" t="inlineStr">
+      <c r="EH20" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EE20">
+      <c r="EI20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EJ20">
         <v>1.248958333333333</v>
       </c>
-      <c r="EF20">
+      <c r="EK20">
         <v>2.100625000000001</v>
       </c>
-      <c r="EG20" t="inlineStr">
+      <c r="EL20" t="inlineStr">
         <is>
           <t>Tsukada (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH20">
+      <c r="EM20">
         <v>2</v>
       </c>
     </row>
@@ -5915,57 +5994,57 @@
           <t>12</t>
         </is>
       </c>
-      <c r="CX21">
+      <c r="DC21">
         <v>1</v>
       </c>
-      <c r="CY21">
+      <c r="DD21">
         <v>12</v>
       </c>
-      <c r="DH21">
+      <c r="DM21">
         <v>1</v>
       </c>
-      <c r="DI21">
+      <c r="DN21">
         <v>12</v>
       </c>
-      <c r="DJ21">
+      <c r="DO21">
         <v>0</v>
       </c>
-      <c r="DK21">
+      <c r="DP21">
         <v>12</v>
       </c>
-      <c r="DL21">
+      <c r="DQ21">
         <v>0</v>
       </c>
-      <c r="DM21">
+      <c r="DR21">
         <v>12</v>
       </c>
-      <c r="DN21">
+      <c r="DS21">
         <v>0</v>
       </c>
-      <c r="DO21">
+      <c r="DT21">
         <v>12</v>
       </c>
-      <c r="EB21" t="inlineStr">
+      <c r="EG21" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC21" t="inlineStr">
+      <c r="EH21" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG21" t="inlineStr">
+      <c r="EI21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL21" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EH21">
+      <c r="EM21">
         <v>2</v>
       </c>
     </row>
@@ -6075,57 +6154,57 @@
           <t>12</t>
         </is>
       </c>
-      <c r="CX22">
+      <c r="DC22">
         <v>1</v>
       </c>
-      <c r="CY22">
+      <c r="DD22">
         <v>12</v>
       </c>
-      <c r="DH22">
+      <c r="DM22">
         <v>0</v>
       </c>
-      <c r="DI22">
+      <c r="DN22">
         <v>12</v>
       </c>
-      <c r="DJ22">
+      <c r="DO22">
         <v>1</v>
       </c>
-      <c r="DK22">
+      <c r="DP22">
         <v>12</v>
       </c>
-      <c r="DL22">
+      <c r="DQ22">
         <v>0</v>
       </c>
-      <c r="DM22">
+      <c r="DR22">
         <v>12</v>
       </c>
-      <c r="DN22">
+      <c r="DS22">
         <v>0</v>
       </c>
-      <c r="DO22">
+      <c r="DT22">
         <v>12</v>
       </c>
-      <c r="EB22" t="inlineStr">
+      <c r="EG22" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC22" t="inlineStr">
+      <c r="EH22" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG22" t="inlineStr">
+      <c r="EI22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL22" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EH22">
+      <c r="EM22">
         <v>2</v>
       </c>
     </row>
@@ -6235,57 +6314,57 @@
           <t>24</t>
         </is>
       </c>
-      <c r="CX23">
+      <c r="DC23">
         <v>1</v>
       </c>
-      <c r="CY23">
+      <c r="DD23">
         <v>24</v>
       </c>
-      <c r="DH23">
+      <c r="DM23">
         <v>0</v>
       </c>
-      <c r="DI23">
+      <c r="DN23">
         <v>24</v>
       </c>
-      <c r="DJ23">
+      <c r="DO23">
         <v>0</v>
       </c>
-      <c r="DK23">
+      <c r="DP23">
         <v>24</v>
       </c>
-      <c r="DL23">
+      <c r="DQ23">
         <v>0</v>
       </c>
-      <c r="DM23">
+      <c r="DR23">
         <v>24</v>
       </c>
-      <c r="DN23">
+      <c r="DS23">
         <v>0</v>
       </c>
-      <c r="DO23">
+      <c r="DT23">
         <v>24</v>
       </c>
-      <c r="EB23" t="inlineStr">
+      <c r="EG23" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC23" t="inlineStr">
+      <c r="EH23" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG23" t="inlineStr">
+      <c r="EI23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL23" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EH23">
+      <c r="EM23">
         <v>2</v>
       </c>
     </row>
@@ -6375,33 +6454,33 @@
           <t>16</t>
         </is>
       </c>
-      <c r="CX24">
+      <c r="DC24">
         <v>6</v>
       </c>
-      <c r="CY24">
+      <c r="DD24">
         <v>15</v>
       </c>
-      <c r="EB24" t="inlineStr">
+      <c r="EG24" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC24" t="inlineStr">
+      <c r="EH24" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG24" t="inlineStr">
+      <c r="EI24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL24" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH24">
+      <c r="EM24">
         <v>3</v>
       </c>
     </row>
@@ -6491,33 +6570,33 @@
           <t>16</t>
         </is>
       </c>
-      <c r="CX25">
+      <c r="DC25">
         <v>1</v>
       </c>
-      <c r="CY25">
+      <c r="DD25">
         <v>13</v>
       </c>
-      <c r="EB25" t="inlineStr">
+      <c r="EG25" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC25" t="inlineStr">
+      <c r="EH25" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG25" t="inlineStr">
+      <c r="EI25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL25" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH25">
+      <c r="EM25">
         <v>3</v>
       </c>
     </row>
@@ -6607,33 +6686,33 @@
           <t>16</t>
         </is>
       </c>
-      <c r="CX26">
+      <c r="DC26">
         <v>2</v>
       </c>
-      <c r="CY26">
+      <c r="DD26">
         <v>14</v>
       </c>
-      <c r="EB26" t="inlineStr">
+      <c r="EG26" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC26" t="inlineStr">
+      <c r="EH26" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG26" t="inlineStr">
+      <c r="EI26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL26" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EH26">
+      <c r="EM26">
         <v>3</v>
       </c>
     </row>
@@ -6756,91 +6835,91 @@
           <t>High</t>
         </is>
       </c>
-      <c r="CG27" t="inlineStr">
+      <c r="CJ27" t="inlineStr">
         <is>
           <t>weight kg</t>
         </is>
       </c>
-      <c r="CH27">
+      <c r="CK27">
         <v>201</v>
       </c>
-      <c r="CJ27">
+      <c r="CN27">
         <v>-1.2</v>
       </c>
-      <c r="CK27">
+      <c r="CO27">
         <v>6.4</v>
       </c>
-      <c r="CL27" t="inlineStr">
+      <c r="CP27" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CM27" t="inlineStr">
+      <c r="CQ27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CN27" t="inlineStr">
+      <c r="CR27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CO27" t="inlineStr">
+      <c r="CS27" t="inlineStr">
         <is>
           <t>52 weeks</t>
         </is>
       </c>
-      <c r="CZ27">
+      <c r="DE27">
         <v>7</v>
       </c>
-      <c r="DA27">
+      <c r="DF27">
         <v>201</v>
       </c>
-      <c r="DB27">
+      <c r="DG27">
         <v>28</v>
       </c>
-      <c r="DC27">
+      <c r="DH27">
         <v>201</v>
       </c>
-      <c r="DJ27">
+      <c r="DO27">
         <v>12</v>
       </c>
-      <c r="DK27">
+      <c r="DP27">
         <v>201</v>
       </c>
-      <c r="DT27">
+      <c r="DY27">
         <v>30</v>
       </c>
-      <c r="DU27">
+      <c r="DZ27">
         <v>201</v>
       </c>
-      <c r="DZ27">
+      <c r="EE27">
         <v>8</v>
       </c>
-      <c r="EA27">
+      <c r="EF27">
         <v>201</v>
       </c>
-      <c r="EB27" t="inlineStr">
+      <c r="EG27" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC27" t="inlineStr">
+      <c r="EH27" t="inlineStr">
         <is>
           <t>&gt;13 weeks</t>
         </is>
       </c>
-      <c r="ED27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG27" t="inlineStr">
+      <c r="EI27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL27" t="inlineStr">
         <is>
           <t>NCT04115319 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH27">
+      <c r="EM27">
         <v>1</v>
       </c>
     </row>
@@ -6963,91 +7042,91 @@
           <t>High</t>
         </is>
       </c>
-      <c r="CG28" t="inlineStr">
+      <c r="CJ28" t="inlineStr">
         <is>
           <t>weight kg</t>
         </is>
       </c>
-      <c r="CH28">
+      <c r="CK28">
         <v>102</v>
       </c>
-      <c r="CJ28">
+      <c r="CN28">
         <v>1.4</v>
       </c>
-      <c r="CK28">
+      <c r="CO28">
         <v>6.4</v>
       </c>
-      <c r="CL28" t="inlineStr">
+      <c r="CP28" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="CM28" t="inlineStr">
+      <c r="CQ28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CN28" t="inlineStr">
+      <c r="CR28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="CO28" t="inlineStr">
+      <c r="CS28" t="inlineStr">
         <is>
           <t>52 weeks</t>
         </is>
       </c>
-      <c r="CZ28">
+      <c r="DE28">
         <v>12</v>
       </c>
-      <c r="DA28">
+      <c r="DF28">
         <v>102</v>
       </c>
-      <c r="DB28">
+      <c r="DG28">
         <v>10</v>
       </c>
-      <c r="DC28">
+      <c r="DH28">
         <v>102</v>
       </c>
-      <c r="DJ28">
+      <c r="DO28">
         <v>21</v>
       </c>
-      <c r="DK28">
+      <c r="DP28">
         <v>102</v>
       </c>
-      <c r="DT28">
+      <c r="DY28">
         <v>11</v>
       </c>
-      <c r="DU28">
+      <c r="DZ28">
         <v>102</v>
       </c>
-      <c r="DZ28">
+      <c r="EE28">
         <v>11</v>
       </c>
-      <c r="EA28">
+      <c r="EF28">
         <v>102</v>
       </c>
-      <c r="EB28" t="inlineStr">
+      <c r="EG28" t="inlineStr">
         <is>
           <t>D2 antipsychotic</t>
         </is>
       </c>
-      <c r="EC28" t="inlineStr">
+      <c r="EH28" t="inlineStr">
         <is>
           <t>&gt;13 weeks</t>
         </is>
       </c>
-      <c r="ED28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG28" t="inlineStr">
+      <c r="EI28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL28" t="inlineStr">
         <is>
           <t>NCT04115319 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EH28">
+      <c r="EM28">
         <v>1</v>
       </c>
     </row>
@@ -7247,24 +7326,22 @@
         <v>6</v>
       </c>
       <c r="AT29">
+        <v>15</v>
+      </c>
+      <c r="AU29">
         <v>19.75</v>
       </c>
-      <c r="AU29">
+      <c r="AV29">
         <v>19.67</v>
       </c>
-      <c r="AV29">
+      <c r="AW29">
         <v>3.61</v>
       </c>
-      <c r="AW29" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7272,99 +7349,107 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
           <t>BNSS total</t>
         </is>
       </c>
-      <c r="BA29">
+      <c r="BB29">
         <v>6</v>
       </c>
-      <c r="BB29">
+      <c r="BC29">
+        <v>15</v>
+      </c>
+      <c r="BD29">
         <v>35.17</v>
       </c>
-      <c r="BC29">
+      <c r="BE29">
         <v>28.17</v>
       </c>
-      <c r="BD29">
+      <c r="BF29">
         <v>20.44</v>
       </c>
-      <c r="BE29" t="inlineStr">
+      <c r="BG29" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX29">
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC29">
         <v>4</v>
       </c>
-      <c r="CY29">
+      <c r="DD29">
         <v>12</v>
       </c>
-      <c r="CZ29">
+      <c r="DE29">
         <v>1</v>
       </c>
-      <c r="DA29">
+      <c r="DF29">
         <v>12</v>
       </c>
-      <c r="DD29">
+      <c r="DI29">
         <v>0</v>
       </c>
-      <c r="DE29">
+      <c r="DJ29">
         <v>12</v>
       </c>
-      <c r="DF29">
+      <c r="DK29">
         <v>0</v>
       </c>
-      <c r="DG29">
+      <c r="DL29">
         <v>12</v>
       </c>
-      <c r="DH29">
+      <c r="DM29">
         <v>2</v>
       </c>
-      <c r="DI29">
+      <c r="DN29">
         <v>12</v>
       </c>
-      <c r="DJ29">
+      <c r="DO29">
         <v>0</v>
       </c>
-      <c r="DK29">
+      <c r="DP29">
         <v>12</v>
       </c>
-      <c r="DT29">
+      <c r="DY29">
         <v>2</v>
       </c>
-      <c r="DU29">
+      <c r="DZ29">
         <v>12</v>
       </c>
-      <c r="EB29" t="inlineStr">
+      <c r="EG29" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC29" t="inlineStr">
+      <c r="EH29" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG29" t="inlineStr">
+      <c r="EI29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL29" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH29">
+      <c r="EM29">
         <v>1</v>
       </c>
     </row>
@@ -7564,24 +7649,22 @@
         <v>10</v>
       </c>
       <c r="AT30">
+        <v>12</v>
+      </c>
+      <c r="AU30">
         <v>17.93</v>
       </c>
-      <c r="AU30">
+      <c r="AV30">
         <v>17.7</v>
       </c>
-      <c r="AV30">
+      <c r="AW30">
         <v>5.25</v>
       </c>
-      <c r="AW30" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7589,99 +7672,107 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
           <t>BNSS total</t>
         </is>
       </c>
-      <c r="BA30">
+      <c r="BB30">
         <v>10</v>
       </c>
-      <c r="BB30">
+      <c r="BC30">
+        <v>12</v>
+      </c>
+      <c r="BD30">
         <v>34.79</v>
       </c>
-      <c r="BC30">
+      <c r="BE30">
         <v>30.4</v>
       </c>
-      <c r="BD30">
+      <c r="BF30">
         <v>12.86</v>
       </c>
-      <c r="BE30" t="inlineStr">
+      <c r="BG30" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX30">
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC30">
         <v>7</v>
       </c>
-      <c r="CY30">
+      <c r="DD30">
         <v>15</v>
       </c>
-      <c r="CZ30">
+      <c r="DE30">
         <v>0</v>
       </c>
-      <c r="DA30">
+      <c r="DF30">
         <v>15</v>
       </c>
-      <c r="DD30">
+      <c r="DI30">
         <v>0</v>
       </c>
-      <c r="DE30">
+      <c r="DJ30">
         <v>15</v>
       </c>
-      <c r="DF30">
+      <c r="DK30">
         <v>0</v>
       </c>
-      <c r="DG30">
+      <c r="DL30">
         <v>15</v>
       </c>
-      <c r="DH30">
+      <c r="DM30">
         <v>0</v>
       </c>
-      <c r="DI30">
+      <c r="DN30">
         <v>15</v>
       </c>
-      <c r="DJ30">
+      <c r="DO30">
         <v>0</v>
       </c>
-      <c r="DK30">
+      <c r="DP30">
         <v>15</v>
       </c>
-      <c r="DT30">
+      <c r="DY30">
         <v>1</v>
       </c>
-      <c r="DU30">
+      <c r="DZ30">
         <v>15</v>
       </c>
-      <c r="EB30" t="inlineStr">
+      <c r="EG30" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="EC30" t="inlineStr">
+      <c r="EH30" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG30" t="inlineStr">
+      <c r="EI30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL30" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH30">
+      <c r="EM30">
         <v>1</v>
       </c>
     </row>
@@ -7881,24 +7972,22 @@
         <v>4</v>
       </c>
       <c r="AT31">
+        <v>5</v>
+      </c>
+      <c r="AU31">
         <v>18</v>
       </c>
-      <c r="AU31">
+      <c r="AV31">
         <v>21.5</v>
       </c>
-      <c r="AV31">
+      <c r="AW31">
         <v>2.6</v>
       </c>
-      <c r="AW31" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>yes</t>
@@ -7906,99 +7995,107 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
           <t>BNSS total</t>
         </is>
       </c>
-      <c r="BA31">
+      <c r="BB31">
         <v>4</v>
       </c>
-      <c r="BB31">
+      <c r="BC31">
+        <v>5</v>
+      </c>
+      <c r="BD31">
         <v>36.4</v>
       </c>
-      <c r="BC31">
+      <c r="BE31">
         <v>33.3</v>
       </c>
-      <c r="BD31">
+      <c r="BF31">
         <v>10.6</v>
       </c>
-      <c r="BE31" t="inlineStr">
+      <c r="BG31" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX31">
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC31">
         <v>2</v>
       </c>
-      <c r="CY31">
+      <c r="DD31">
         <v>5</v>
       </c>
-      <c r="CZ31">
+      <c r="DE31">
         <v>0</v>
       </c>
-      <c r="DA31">
+      <c r="DF31">
         <v>5</v>
       </c>
-      <c r="DD31">
+      <c r="DI31">
         <v>1</v>
       </c>
-      <c r="DE31">
+      <c r="DJ31">
         <v>5</v>
       </c>
-      <c r="DF31">
+      <c r="DK31">
         <v>0</v>
       </c>
-      <c r="DG31">
+      <c r="DL31">
         <v>5</v>
       </c>
-      <c r="DH31">
+      <c r="DM31">
         <v>0</v>
       </c>
-      <c r="DI31">
+      <c r="DN31">
         <v>5</v>
       </c>
-      <c r="DJ31">
+      <c r="DO31">
         <v>0</v>
       </c>
-      <c r="DK31">
+      <c r="DP31">
         <v>5</v>
       </c>
-      <c r="DT31">
+      <c r="DY31">
         <v>0</v>
       </c>
-      <c r="DU31">
+      <c r="DZ31">
         <v>5</v>
       </c>
-      <c r="EB31" t="inlineStr">
+      <c r="EG31" t="inlineStr">
         <is>
           <t>TAAR1 agonist (add-on)</t>
         </is>
       </c>
-      <c r="EC31" t="inlineStr">
+      <c r="EH31" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG31" t="inlineStr">
+      <c r="EI31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL31" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH31">
+      <c r="EM31">
         <v>1</v>
       </c>
     </row>
@@ -8198,24 +8295,22 @@
         <v>20</v>
       </c>
       <c r="AT32">
+        <v>30</v>
+      </c>
+      <c r="AU32">
         <v>17.6</v>
       </c>
-      <c r="AU32">
+      <c r="AV32">
         <v>16.5</v>
       </c>
-      <c r="AV32">
+      <c r="AW32">
         <v>4.7</v>
       </c>
-      <c r="AW32" t="inlineStr">
+      <c r="AX32" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8223,99 +8318,107 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
           <t>BNSS total</t>
         </is>
       </c>
-      <c r="BA32">
+      <c r="BB32">
         <v>19</v>
       </c>
-      <c r="BB32">
+      <c r="BC32">
+        <v>30</v>
+      </c>
+      <c r="BD32">
         <v>38.1</v>
       </c>
-      <c r="BC32">
+      <c r="BE32">
         <v>29.6</v>
       </c>
-      <c r="BD32">
+      <c r="BF32">
         <v>9.199999999999999</v>
       </c>
-      <c r="BE32" t="inlineStr">
+      <c r="BG32" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX32">
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC32">
         <v>8</v>
       </c>
-      <c r="CY32">
+      <c r="DD32">
         <v>30</v>
       </c>
-      <c r="CZ32">
+      <c r="DE32">
         <v>1</v>
       </c>
-      <c r="DA32">
+      <c r="DF32">
         <v>30</v>
       </c>
-      <c r="DD32">
+      <c r="DI32">
         <v>2</v>
       </c>
-      <c r="DE32">
+      <c r="DJ32">
         <v>30</v>
       </c>
-      <c r="DF32">
+      <c r="DK32">
         <v>1</v>
       </c>
-      <c r="DG32">
+      <c r="DL32">
         <v>30</v>
       </c>
-      <c r="DH32">
+      <c r="DM32">
         <v>1</v>
       </c>
-      <c r="DI32">
+      <c r="DN32">
         <v>30</v>
       </c>
-      <c r="DJ32">
+      <c r="DO32">
         <v>2</v>
       </c>
-      <c r="DK32">
+      <c r="DP32">
         <v>30</v>
       </c>
-      <c r="DT32">
+      <c r="DY32">
         <v>0</v>
       </c>
-      <c r="DU32">
+      <c r="DZ32">
         <v>30</v>
       </c>
-      <c r="EB32" t="inlineStr">
+      <c r="EG32" t="inlineStr">
         <is>
           <t>TAAR1 agonist (add-on)</t>
         </is>
       </c>
-      <c r="EC32" t="inlineStr">
+      <c r="EH32" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG32" t="inlineStr">
+      <c r="EI32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL32" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH32">
+      <c r="EM32">
         <v>1</v>
       </c>
     </row>
@@ -8515,24 +8618,22 @@
         <v>21</v>
       </c>
       <c r="AT33">
+        <v>32</v>
+      </c>
+      <c r="AU33">
         <v>17.2</v>
       </c>
-      <c r="AU33">
+      <c r="AV33">
         <v>15.5</v>
       </c>
-      <c r="AV33">
+      <c r="AW33">
         <v>4.3</v>
       </c>
-      <c r="AW33" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8540,99 +8641,107 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
           <t>BNSS total</t>
         </is>
       </c>
-      <c r="BA33">
+      <c r="BB33">
         <v>21</v>
       </c>
-      <c r="BB33">
+      <c r="BC33">
+        <v>32</v>
+      </c>
+      <c r="BD33">
         <v>38.4</v>
       </c>
-      <c r="BC33">
+      <c r="BE33">
         <v>29.2</v>
       </c>
-      <c r="BD33">
+      <c r="BF33">
         <v>12.4</v>
       </c>
-      <c r="BE33" t="inlineStr">
+      <c r="BG33" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX33">
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC33">
         <v>4</v>
       </c>
-      <c r="CY33">
+      <c r="DD33">
         <v>32</v>
       </c>
-      <c r="CZ33">
+      <c r="DE33">
         <v>0</v>
       </c>
-      <c r="DA33">
+      <c r="DF33">
         <v>32</v>
       </c>
-      <c r="DD33">
+      <c r="DI33">
         <v>1</v>
       </c>
-      <c r="DE33">
+      <c r="DJ33">
         <v>32</v>
       </c>
-      <c r="DF33">
+      <c r="DK33">
         <v>0</v>
       </c>
-      <c r="DG33">
+      <c r="DL33">
         <v>32</v>
       </c>
-      <c r="DH33">
+      <c r="DM33">
         <v>1</v>
       </c>
-      <c r="DI33">
+      <c r="DN33">
         <v>32</v>
       </c>
-      <c r="DJ33">
+      <c r="DO33">
         <v>0</v>
       </c>
-      <c r="DK33">
+      <c r="DP33">
         <v>32</v>
       </c>
-      <c r="DT33">
+      <c r="DY33">
         <v>0</v>
       </c>
-      <c r="DU33">
+      <c r="DZ33">
         <v>32</v>
       </c>
-      <c r="EB33" t="inlineStr">
+      <c r="EG33" t="inlineStr">
         <is>
           <t>TAAR1 agonist (add-on)</t>
         </is>
       </c>
-      <c r="EC33" t="inlineStr">
+      <c r="EH33" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG33" t="inlineStr">
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL33" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH33">
+      <c r="EM33">
         <v>1</v>
       </c>
     </row>
@@ -8832,24 +8941,22 @@
         <v>31</v>
       </c>
       <c r="AT34">
+        <v>37</v>
+      </c>
+      <c r="AU34">
         <v>18.9</v>
       </c>
-      <c r="AU34">
+      <c r="AV34">
         <v>17.3</v>
       </c>
-      <c r="AV34">
+      <c r="AW34">
         <v>4.5</v>
       </c>
-      <c r="AW34" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>yes</t>
@@ -8857,99 +8964,107 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
           <t>BNSS total</t>
         </is>
       </c>
-      <c r="BA34">
+      <c r="BB34">
         <v>31</v>
       </c>
-      <c r="BB34">
+      <c r="BC34">
+        <v>37</v>
+      </c>
+      <c r="BD34">
         <v>36.6</v>
       </c>
-      <c r="BC34">
+      <c r="BE34">
         <v>32.7</v>
       </c>
-      <c r="BD34">
+      <c r="BF34">
         <v>13.4</v>
       </c>
-      <c r="BE34" t="inlineStr">
+      <c r="BG34" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="CX34">
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="DC34">
         <v>9</v>
       </c>
-      <c r="CY34">
+      <c r="DD34">
         <v>37</v>
       </c>
-      <c r="CZ34">
+      <c r="DE34">
         <v>0</v>
       </c>
-      <c r="DA34">
+      <c r="DF34">
         <v>37</v>
       </c>
-      <c r="DD34">
+      <c r="DI34">
         <v>1</v>
       </c>
-      <c r="DE34">
+      <c r="DJ34">
         <v>37</v>
       </c>
-      <c r="DF34">
+      <c r="DK34">
         <v>3</v>
       </c>
-      <c r="DG34">
+      <c r="DL34">
         <v>37</v>
       </c>
-      <c r="DH34">
+      <c r="DM34">
         <v>2</v>
       </c>
-      <c r="DI34">
+      <c r="DN34">
         <v>37</v>
       </c>
-      <c r="DJ34">
+      <c r="DO34">
         <v>2</v>
       </c>
-      <c r="DK34">
+      <c r="DP34">
         <v>37</v>
       </c>
-      <c r="DT34">
+      <c r="DY34">
         <v>0</v>
       </c>
-      <c r="DU34">
+      <c r="DZ34">
         <v>37</v>
       </c>
-      <c r="EB34" t="inlineStr">
+      <c r="EG34" t="inlineStr">
         <is>
           <t>placebo (add-on)</t>
         </is>
       </c>
-      <c r="EC34" t="inlineStr">
+      <c r="EH34" t="inlineStr">
         <is>
           <t>3-13 weeks</t>
         </is>
       </c>
-      <c r="ED34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG34" t="inlineStr">
+      <c r="EI34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL34" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EH34">
+      <c r="EM34">
         <v>1</v>
       </c>
     </row>
@@ -9044,57 +9159,57 @@
           <t>29</t>
         </is>
       </c>
-      <c r="CX35">
+      <c r="DC35">
         <v>20</v>
       </c>
-      <c r="CY35">
+      <c r="DD35">
         <v>29</v>
       </c>
-      <c r="DD35">
+      <c r="DI35">
         <v>4</v>
       </c>
-      <c r="DE35">
+      <c r="DJ35">
         <v>29</v>
       </c>
-      <c r="DH35">
+      <c r="DM35">
         <v>8</v>
       </c>
-      <c r="DI35">
+      <c r="DN35">
         <v>29</v>
       </c>
-      <c r="DJ35">
+      <c r="DO35">
         <v>4</v>
       </c>
-      <c r="DK35">
+      <c r="DP35">
         <v>29</v>
       </c>
-      <c r="DN35">
+      <c r="DS35">
         <v>0</v>
       </c>
-      <c r="DO35">
+      <c r="DT35">
         <v>29</v>
       </c>
-      <c r="EB35" t="inlineStr">
+      <c r="EG35" t="inlineStr">
         <is>
           <t>TAAR1 agonist</t>
         </is>
       </c>
-      <c r="EC35" t="inlineStr">
+      <c r="EH35" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG35" t="inlineStr">
+      <c r="EI35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL35" t="inlineStr">
         <is>
           <t>NCT05402111 (2022) - ulotaront</t>
         </is>
       </c>
-      <c r="EH35">
+      <c r="EM35">
         <v>1</v>
       </c>
     </row>
@@ -9184,57 +9299,57 @@
           <t>26</t>
         </is>
       </c>
-      <c r="CX36">
+      <c r="DC36">
         <v>9</v>
       </c>
-      <c r="CY36">
+      <c r="DD36">
         <v>26</v>
       </c>
-      <c r="DD36">
+      <c r="DI36">
         <v>0</v>
       </c>
-      <c r="DE36">
+      <c r="DJ36">
         <v>26</v>
       </c>
-      <c r="DH36">
+      <c r="DM36">
         <v>0</v>
       </c>
-      <c r="DI36">
+      <c r="DN36">
         <v>26</v>
       </c>
-      <c r="DJ36">
+      <c r="DO36">
         <v>1</v>
       </c>
-      <c r="DK36">
+      <c r="DP36">
         <v>26</v>
       </c>
-      <c r="DN36">
+      <c r="DS36">
         <v>0</v>
       </c>
-      <c r="DO36">
+      <c r="DT36">
         <v>26</v>
       </c>
-      <c r="EB36" t="inlineStr">
+      <c r="EG36" t="inlineStr">
         <is>
           <t>D2 antipsychotic</t>
         </is>
       </c>
-      <c r="EC36" t="inlineStr">
+      <c r="EH36" t="inlineStr">
         <is>
           <t>1 day-2 weeks</t>
         </is>
       </c>
-      <c r="ED36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EG36" t="inlineStr">
+      <c r="EI36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EL36" t="inlineStr">
         <is>
           <t>NCT05402111 (2022) - ulotaront</t>
         </is>
       </c>
-      <c r="EH36">
+      <c r="EM36">
         <v>1</v>
       </c>
     </row>

--- a/data_u1/data_2025-01-16_LSR3_H.xlsx
+++ b/data_u1/data_2025-01-16_LSR3_H.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:EM36"/>
+  <dimension ref="A1:EL36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -837,235 +837,230 @@
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>Timepoint</t>
+          <t>prolactin_scale_name</t>
         </is>
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>prolactin_scale_name</t>
+          <t>prolactin_n</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
         <is>
-          <t>prolactin_n</t>
+          <t>prolactin_baseline_n</t>
         </is>
       </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>prolactin_baseline_n</t>
+          <t>prolactin_baseline</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>prolactin_baseline</t>
+          <t>prolactin_mean</t>
         </is>
       </c>
       <c r="CX1" s="1" t="inlineStr">
         <is>
-          <t>prolactin_mean</t>
+          <t>prolactin_sd</t>
         </is>
       </c>
       <c r="CY1" s="1" t="inlineStr">
         <is>
-          <t>prolactin_sd</t>
+          <t>prolactin_change_endpoint</t>
         </is>
       </c>
       <c r="CZ1" s="1" t="inlineStr">
         <is>
-          <t>prolactin_change_endpoint</t>
+          <t>prolactin_completer</t>
         </is>
       </c>
       <c r="DA1" s="1" t="inlineStr">
         <is>
-          <t>prolactin_completer</t>
+          <t>prolactin_sd_origin</t>
         </is>
       </c>
       <c r="DB1" s="1" t="inlineStr">
         <is>
-          <t>prolactin_sd_origin</t>
+          <t>adverse_event_e</t>
         </is>
       </c>
       <c r="DC1" s="1" t="inlineStr">
         <is>
-          <t>adverse_event_e</t>
+          <t>adverse_event_n</t>
         </is>
       </c>
       <c r="DD1" s="1" t="inlineStr">
         <is>
-          <t>adverse_event_n</t>
+          <t>anticholinergic_symptom_e</t>
         </is>
       </c>
       <c r="DE1" s="1" t="inlineStr">
         <is>
-          <t>anticholinergic_symptom_e</t>
+          <t>anticholinergic_symptom_n</t>
         </is>
       </c>
       <c r="DF1" s="1" t="inlineStr">
         <is>
-          <t>anticholinergic_symptom_n</t>
+          <t>anxiety_e</t>
         </is>
       </c>
       <c r="DG1" s="1" t="inlineStr">
         <is>
-          <t>anxiety_e</t>
+          <t>anxiety_n</t>
         </is>
       </c>
       <c r="DH1" s="1" t="inlineStr">
         <is>
-          <t>anxiety_n</t>
+          <t>dizziness_e</t>
         </is>
       </c>
       <c r="DI1" s="1" t="inlineStr">
         <is>
-          <t>dizziness_e</t>
+          <t>dizziness_n</t>
         </is>
       </c>
       <c r="DJ1" s="1" t="inlineStr">
         <is>
-          <t>dizziness_n</t>
+          <t>headache_e</t>
         </is>
       </c>
       <c r="DK1" s="1" t="inlineStr">
         <is>
-          <t>headache_e</t>
+          <t>headache_n</t>
         </is>
       </c>
       <c r="DL1" s="1" t="inlineStr">
         <is>
-          <t>headache_n</t>
+          <t>nausea_vomitting_e</t>
         </is>
       </c>
       <c r="DM1" s="1" t="inlineStr">
         <is>
-          <t>nausea_vomitting_e</t>
+          <t>nausea_vomitting_n</t>
         </is>
       </c>
       <c r="DN1" s="1" t="inlineStr">
         <is>
-          <t>nausea_vomitting_n</t>
+          <t>sedation_e</t>
         </is>
       </c>
       <c r="DO1" s="1" t="inlineStr">
         <is>
-          <t>sedation_e</t>
+          <t>sedation_n</t>
         </is>
       </c>
       <c r="DP1" s="1" t="inlineStr">
         <is>
-          <t>sedation_n</t>
+          <t>hyperprolactinemia_e</t>
         </is>
       </c>
       <c r="DQ1" s="1" t="inlineStr">
         <is>
-          <t>hyperprolactinemia_e</t>
+          <t>hyperprolactinemia_n</t>
         </is>
       </c>
       <c r="DR1" s="1" t="inlineStr">
         <is>
-          <t>hyperprolactinemia_n</t>
+          <t>qtc_prolongation_e</t>
         </is>
       </c>
       <c r="DS1" s="1" t="inlineStr">
         <is>
-          <t>qtc_prolongation_e</t>
+          <t>qtc_prolongation_n</t>
         </is>
       </c>
       <c r="DT1" s="1" t="inlineStr">
         <is>
-          <t>qtc_prolongation_n</t>
+          <t>agitation_e</t>
         </is>
       </c>
       <c r="DU1" s="1" t="inlineStr">
         <is>
-          <t>agitation_e</t>
+          <t>agitation_n</t>
         </is>
       </c>
       <c r="DV1" s="1" t="inlineStr">
         <is>
-          <t>agitation_n</t>
+          <t>hypotension_e</t>
         </is>
       </c>
       <c r="DW1" s="1" t="inlineStr">
         <is>
-          <t>hypotension_e</t>
+          <t>hypotension_n</t>
         </is>
       </c>
       <c r="DX1" s="1" t="inlineStr">
         <is>
-          <t>hypotension_n</t>
+          <t>insomnia_e</t>
         </is>
       </c>
       <c r="DY1" s="1" t="inlineStr">
         <is>
-          <t>insomnia_e</t>
+          <t>insomnia_n</t>
         </is>
       </c>
       <c r="DZ1" s="1" t="inlineStr">
         <is>
-          <t>insomnia_n</t>
+          <t>akathisia_e</t>
         </is>
       </c>
       <c r="EA1" s="1" t="inlineStr">
         <is>
-          <t>akathisia_e</t>
+          <t>akathisia_n</t>
         </is>
       </c>
       <c r="EB1" s="1" t="inlineStr">
         <is>
-          <t>akathisia_n</t>
+          <t>eps_symptoms_e</t>
         </is>
       </c>
       <c r="EC1" s="1" t="inlineStr">
         <is>
-          <t>eps_symptoms_e</t>
+          <t>eps_symptoms_n</t>
         </is>
       </c>
       <c r="ED1" s="1" t="inlineStr">
         <is>
-          <t>eps_symptoms_n</t>
+          <t>weight_increased_e</t>
         </is>
       </c>
       <c r="EE1" s="1" t="inlineStr">
         <is>
-          <t>weight_increased_e</t>
+          <t>weight_increased_n</t>
         </is>
       </c>
       <c r="EF1" s="1" t="inlineStr">
         <is>
-          <t>weight_increased_n</t>
+          <t>drug_new</t>
         </is>
       </c>
       <c r="EG1" s="1" t="inlineStr">
         <is>
-          <t>drug_new</t>
+          <t>timepoint</t>
         </is>
       </c>
       <c r="EH1" s="1" t="inlineStr">
         <is>
-          <t>timepoint</t>
+          <t>comparison_data</t>
         </is>
       </c>
       <c r="EI1" s="1" t="inlineStr">
         <is>
-          <t>comparison_data</t>
+          <t>qtc_md_point</t>
         </is>
       </c>
       <c r="EJ1" s="1" t="inlineStr">
         <is>
-          <t>qtc_md_point</t>
+          <t>qtc_md_se</t>
         </is>
       </c>
       <c r="EK1" s="1" t="inlineStr">
         <is>
-          <t>qtc_md_se</t>
+          <t>study_name_drug</t>
         </is>
       </c>
       <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>study_name_drug</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>crossover_periods</t>
         </is>
@@ -1321,60 +1316,60 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB2">
+        <v>18</v>
+      </c>
       <c r="DC2">
-        <v>18</v>
-      </c>
-      <c r="DD2">
         <v>25</v>
       </c>
+      <c r="DH2">
+        <v>4</v>
+      </c>
       <c r="DI2">
-        <v>4</v>
-      </c>
-      <c r="DJ2">
         <v>25</v>
       </c>
+      <c r="DL2">
+        <v>3</v>
+      </c>
       <c r="DM2">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="DN2">
+        <v>2</v>
+      </c>
+      <c r="DO2">
         <v>25</v>
       </c>
-      <c r="DO2">
+      <c r="DV2">
+        <v>13</v>
+      </c>
+      <c r="DW2">
+        <v>25</v>
+      </c>
+      <c r="DX2">
         <v>2</v>
       </c>
-      <c r="DP2">
-        <v>25</v>
-      </c>
-      <c r="DW2">
-        <v>13</v>
-      </c>
-      <c r="DX2">
-        <v>25</v>
-      </c>
-      <c r="DY2">
-        <v>2</v>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
         <is>
           <t>Isaacson (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM2">
+      <c r="EL2">
         <v>1</v>
       </c>
     </row>
@@ -1628,75 +1623,75 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB3">
+        <v>12</v>
+      </c>
       <c r="DC3">
-        <v>12</v>
-      </c>
-      <c r="DD3">
         <v>14</v>
       </c>
+      <c r="DF3">
+        <v>0</v>
+      </c>
       <c r="DG3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="DH3">
+        <v>1</v>
+      </c>
+      <c r="DI3">
         <v>14</v>
       </c>
-      <c r="DI3">
+      <c r="DL3">
         <v>1</v>
       </c>
-      <c r="DJ3">
+      <c r="DM3">
         <v>14</v>
       </c>
-      <c r="DM3">
+      <c r="DN3">
+        <v>2</v>
+      </c>
+      <c r="DO3">
+        <v>14</v>
+      </c>
+      <c r="DT3">
         <v>1</v>
       </c>
-      <c r="DN3">
+      <c r="DU3">
         <v>14</v>
       </c>
-      <c r="DO3">
-        <v>2</v>
-      </c>
-      <c r="DP3">
+      <c r="DV3">
+        <v>11</v>
+      </c>
+      <c r="DW3">
         <v>14</v>
       </c>
-      <c r="DU3">
+      <c r="DX3">
         <v>1</v>
       </c>
-      <c r="DV3">
+      <c r="DY3">
         <v>14</v>
       </c>
-      <c r="DW3">
-        <v>11</v>
-      </c>
-      <c r="DX3">
-        <v>14</v>
-      </c>
-      <c r="DY3">
-        <v>1</v>
-      </c>
-      <c r="DZ3">
-        <v>14</v>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
       </c>
       <c r="EG3" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH3" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL3" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
         <is>
           <t>Isaacson (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM3">
+      <c r="EL3">
         <v>1</v>
       </c>
     </row>
@@ -2028,125 +2023,120 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>4 weeks</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
           <t>prolactin levels ng/ml</t>
         </is>
       </c>
-      <c r="CU4">
+      <c r="CT4">
         <v>114</v>
       </c>
+      <c r="CW4">
+        <v>-1.965789473684211</v>
+      </c>
       <c r="CX4">
-        <v>-1.965789473684211</v>
-      </c>
-      <c r="CY4">
         <v>28</v>
       </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>change</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DB4" t="inlineStr">
-        <is>
           <t>no</t>
         </is>
       </c>
+      <c r="DB4">
+        <v>55</v>
+      </c>
       <c r="DC4">
-        <v>55</v>
-      </c>
-      <c r="DD4">
         <v>120</v>
       </c>
+      <c r="DF4">
+        <v>2</v>
+      </c>
       <c r="DG4">
-        <v>2</v>
-      </c>
-      <c r="DH4">
         <v>120</v>
       </c>
+      <c r="DJ4">
+        <v>11</v>
+      </c>
       <c r="DK4">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="DL4">
+        <v>6</v>
+      </c>
+      <c r="DM4">
         <v>120</v>
       </c>
-      <c r="DM4">
+      <c r="DN4">
+        <v>8</v>
+      </c>
+      <c r="DO4">
+        <v>120</v>
+      </c>
+      <c r="DR4">
+        <v>0</v>
+      </c>
+      <c r="DS4">
+        <v>120</v>
+      </c>
+      <c r="DT4">
         <v>6</v>
       </c>
-      <c r="DN4">
+      <c r="DU4">
         <v>120</v>
       </c>
-      <c r="DO4">
-        <v>8</v>
-      </c>
-      <c r="DP4">
+      <c r="DX4">
+        <v>4</v>
+      </c>
+      <c r="DY4">
         <v>120</v>
       </c>
-      <c r="DS4">
-        <v>0</v>
-      </c>
-      <c r="DT4">
+      <c r="DZ4">
+        <v>1</v>
+      </c>
+      <c r="EA4">
         <v>120</v>
       </c>
-      <c r="DU4">
-        <v>6</v>
-      </c>
-      <c r="DV4">
+      <c r="EB4">
+        <v>4</v>
+      </c>
+      <c r="EC4">
         <v>120</v>
       </c>
-      <c r="DY4">
-        <v>4</v>
-      </c>
-      <c r="DZ4">
+      <c r="ED4">
+        <v>1</v>
+      </c>
+      <c r="EE4">
         <v>120</v>
       </c>
-      <c r="EA4">
-        <v>1</v>
-      </c>
-      <c r="EB4">
-        <v>120</v>
-      </c>
-      <c r="EC4">
-        <v>4</v>
-      </c>
-      <c r="ED4">
-        <v>120</v>
-      </c>
-      <c r="EE4">
-        <v>1</v>
-      </c>
-      <c r="EF4">
-        <v>120</v>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG4" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH4" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL4" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
         <is>
           <t>Koblan (2020) - ulotaront</t>
         </is>
       </c>
-      <c r="EM4">
+      <c r="EL4">
         <v>1</v>
       </c>
     </row>
@@ -2478,125 +2468,120 @@
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>4 weeks</t>
-        </is>
-      </c>
-      <c r="CT5" t="inlineStr">
-        <is>
           <t>prolactin levels ng/ml</t>
         </is>
       </c>
-      <c r="CU5">
+      <c r="CT5">
         <v>113</v>
       </c>
+      <c r="CW5">
+        <v>-1.383805309734513</v>
+      </c>
       <c r="CX5">
-        <v>-1.383805309734513</v>
-      </c>
-      <c r="CY5">
         <v>28</v>
       </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>change</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="DB5" t="inlineStr">
-        <is>
           <t>no</t>
         </is>
       </c>
+      <c r="DB5">
+        <v>63</v>
+      </c>
       <c r="DC5">
-        <v>63</v>
-      </c>
-      <c r="DD5">
         <v>125</v>
       </c>
+      <c r="DF5">
+        <v>9</v>
+      </c>
       <c r="DG5">
-        <v>9</v>
-      </c>
-      <c r="DH5">
         <v>125</v>
       </c>
+      <c r="DJ5">
+        <v>15</v>
+      </c>
       <c r="DK5">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="DL5">
+        <v>4</v>
+      </c>
+      <c r="DM5">
         <v>125</v>
       </c>
-      <c r="DM5">
+      <c r="DN5">
+        <v>6</v>
+      </c>
+      <c r="DO5">
+        <v>125</v>
+      </c>
+      <c r="DR5">
+        <v>0</v>
+      </c>
+      <c r="DS5">
+        <v>125</v>
+      </c>
+      <c r="DT5">
+        <v>6</v>
+      </c>
+      <c r="DU5">
+        <v>125</v>
+      </c>
+      <c r="DX5">
+        <v>13</v>
+      </c>
+      <c r="DY5">
+        <v>125</v>
+      </c>
+      <c r="DZ5">
+        <v>0</v>
+      </c>
+      <c r="EA5">
+        <v>125</v>
+      </c>
+      <c r="EB5">
         <v>4</v>
       </c>
-      <c r="DN5">
+      <c r="EC5">
         <v>125</v>
       </c>
-      <c r="DO5">
-        <v>6</v>
-      </c>
-      <c r="DP5">
+      <c r="ED5">
+        <v>1</v>
+      </c>
+      <c r="EE5">
         <v>125</v>
       </c>
-      <c r="DS5">
-        <v>0</v>
-      </c>
-      <c r="DT5">
-        <v>125</v>
-      </c>
-      <c r="DU5">
-        <v>6</v>
-      </c>
-      <c r="DV5">
-        <v>125</v>
-      </c>
-      <c r="DY5">
-        <v>13</v>
-      </c>
-      <c r="DZ5">
-        <v>125</v>
-      </c>
-      <c r="EA5">
-        <v>0</v>
-      </c>
-      <c r="EB5">
-        <v>125</v>
-      </c>
-      <c r="EC5">
-        <v>4</v>
-      </c>
-      <c r="ED5">
-        <v>125</v>
-      </c>
-      <c r="EE5">
-        <v>1</v>
-      </c>
-      <c r="EF5">
-        <v>125</v>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL5" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
         <is>
           <t>Koblan (2020) - ulotaront</t>
         </is>
       </c>
-      <c r="EM5">
+      <c r="EL5">
         <v>1</v>
       </c>
     </row>
@@ -2748,27 +2733,27 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
+      </c>
       <c r="EG6" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH6" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL6" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EM6">
+      <c r="EL6">
         <v>1</v>
       </c>
     </row>
@@ -2920,27 +2905,27 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
+      </c>
       <c r="EG7" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH7" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL7" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EM7">
+      <c r="EL7">
         <v>1</v>
       </c>
     </row>
@@ -3092,27 +3077,27 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
       <c r="EG8" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL8" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
         <is>
           <t>NCT04072354 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EM8">
+      <c r="EL8">
         <v>1</v>
       </c>
     </row>
@@ -3264,27 +3249,27 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
+      </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL9" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EM9">
+      <c r="EL9">
         <v>1</v>
       </c>
     </row>
@@ -3436,27 +3421,27 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
+      </c>
       <c r="EG10" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH10" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL10" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EM10">
+      <c r="EL10">
         <v>1</v>
       </c>
     </row>
@@ -3608,27 +3593,27 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
       <c r="EG11" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH11" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL11" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK11" t="inlineStr">
         <is>
           <t>NCT04092686 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EM11">
+      <c r="EL11">
         <v>1</v>
       </c>
     </row>
@@ -3918,69 +3903,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB12">
+        <v>23</v>
+      </c>
       <c r="DC12">
-        <v>23</v>
-      </c>
-      <c r="DD12">
         <v>72</v>
       </c>
+      <c r="DF12">
+        <v>6</v>
+      </c>
       <c r="DG12">
-        <v>6</v>
-      </c>
-      <c r="DH12">
         <v>72</v>
       </c>
+      <c r="DJ12">
+        <v>4</v>
+      </c>
       <c r="DK12">
+        <v>72</v>
+      </c>
+      <c r="DL12">
         <v>4</v>
       </c>
-      <c r="DL12">
+      <c r="DM12">
         <v>72</v>
       </c>
-      <c r="DM12">
-        <v>4</v>
-      </c>
-      <c r="DN12">
+      <c r="DT12">
+        <v>2</v>
+      </c>
+      <c r="DU12">
         <v>72</v>
       </c>
-      <c r="DU12">
-        <v>2</v>
-      </c>
-      <c r="DV12">
+      <c r="DX12">
+        <v>1</v>
+      </c>
+      <c r="DY12">
         <v>72</v>
       </c>
-      <c r="DY12">
+      <c r="ED12">
         <v>1</v>
       </c>
-      <c r="DZ12">
+      <c r="EE12">
         <v>72</v>
       </c>
-      <c r="EE12">
-        <v>1</v>
-      </c>
-      <c r="EF12">
-        <v>72</v>
+      <c r="EF12" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
       </c>
       <c r="EG12" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH12" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL12" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK12" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM12">
+      <c r="EL12">
         <v>1</v>
       </c>
     </row>
@@ -4270,69 +4255,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB13">
+        <v>14</v>
+      </c>
       <c r="DC13">
-        <v>14</v>
-      </c>
-      <c r="DD13">
         <v>65</v>
       </c>
+      <c r="DF13">
+        <v>3</v>
+      </c>
       <c r="DG13">
+        <v>65</v>
+      </c>
+      <c r="DJ13">
+        <v>4</v>
+      </c>
+      <c r="DK13">
+        <v>65</v>
+      </c>
+      <c r="DL13">
+        <v>0</v>
+      </c>
+      <c r="DM13">
+        <v>65</v>
+      </c>
+      <c r="DT13">
+        <v>0</v>
+      </c>
+      <c r="DU13">
+        <v>65</v>
+      </c>
+      <c r="DX13">
         <v>3</v>
       </c>
-      <c r="DH13">
+      <c r="DY13">
         <v>65</v>
       </c>
-      <c r="DK13">
-        <v>4</v>
-      </c>
-      <c r="DL13">
+      <c r="ED13">
+        <v>2</v>
+      </c>
+      <c r="EE13">
         <v>65</v>
       </c>
-      <c r="DM13">
-        <v>0</v>
-      </c>
-      <c r="DN13">
-        <v>65</v>
-      </c>
-      <c r="DU13">
-        <v>0</v>
-      </c>
-      <c r="DV13">
-        <v>65</v>
-      </c>
-      <c r="DY13">
-        <v>3</v>
-      </c>
-      <c r="DZ13">
-        <v>65</v>
-      </c>
-      <c r="EE13">
-        <v>2</v>
-      </c>
-      <c r="EF13">
-        <v>65</v>
+      <c r="EF13" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG13" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH13" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL13" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK13" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM13">
+      <c r="EL13">
         <v>1</v>
       </c>
     </row>
@@ -4622,69 +4607,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB14">
+        <v>23</v>
+      </c>
       <c r="DC14">
-        <v>23</v>
-      </c>
-      <c r="DD14">
         <v>68</v>
       </c>
+      <c r="DF14">
+        <v>2</v>
+      </c>
       <c r="DG14">
+        <v>68</v>
+      </c>
+      <c r="DJ14">
+        <v>5</v>
+      </c>
+      <c r="DK14">
+        <v>68</v>
+      </c>
+      <c r="DL14">
         <v>2</v>
       </c>
-      <c r="DH14">
+      <c r="DM14">
         <v>68</v>
       </c>
-      <c r="DK14">
+      <c r="DT14">
+        <v>8</v>
+      </c>
+      <c r="DU14">
+        <v>68</v>
+      </c>
+      <c r="DX14">
         <v>5</v>
       </c>
-      <c r="DL14">
+      <c r="DY14">
         <v>68</v>
       </c>
-      <c r="DM14">
-        <v>2</v>
-      </c>
-      <c r="DN14">
+      <c r="ED14">
+        <v>0</v>
+      </c>
+      <c r="EE14">
         <v>68</v>
       </c>
-      <c r="DU14">
-        <v>8</v>
-      </c>
-      <c r="DV14">
-        <v>68</v>
-      </c>
-      <c r="DY14">
-        <v>5</v>
-      </c>
-      <c r="DZ14">
-        <v>68</v>
-      </c>
-      <c r="EE14">
-        <v>0</v>
-      </c>
-      <c r="EF14">
-        <v>68</v>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG14" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH14" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL14" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK14" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM14">
+      <c r="EL14">
         <v>1</v>
       </c>
     </row>
@@ -4974,69 +4959,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB15">
+        <v>36</v>
+      </c>
       <c r="DC15">
-        <v>36</v>
-      </c>
-      <c r="DD15">
         <v>71</v>
       </c>
+      <c r="DF15">
+        <v>5</v>
+      </c>
       <c r="DG15">
+        <v>71</v>
+      </c>
+      <c r="DJ15">
+        <v>6</v>
+      </c>
+      <c r="DK15">
+        <v>71</v>
+      </c>
+      <c r="DL15">
+        <v>6</v>
+      </c>
+      <c r="DM15">
+        <v>71</v>
+      </c>
+      <c r="DT15">
+        <v>0</v>
+      </c>
+      <c r="DU15">
+        <v>71</v>
+      </c>
+      <c r="DX15">
         <v>5</v>
       </c>
-      <c r="DH15">
+      <c r="DY15">
         <v>71</v>
       </c>
-      <c r="DK15">
-        <v>6</v>
-      </c>
-      <c r="DL15">
+      <c r="ED15">
+        <v>8</v>
+      </c>
+      <c r="EE15">
         <v>71</v>
       </c>
-      <c r="DM15">
-        <v>6</v>
-      </c>
-      <c r="DN15">
-        <v>71</v>
-      </c>
-      <c r="DU15">
-        <v>0</v>
-      </c>
-      <c r="DV15">
-        <v>71</v>
-      </c>
-      <c r="DY15">
-        <v>5</v>
-      </c>
-      <c r="DZ15">
-        <v>71</v>
-      </c>
-      <c r="EE15">
-        <v>8</v>
-      </c>
-      <c r="EF15">
-        <v>71</v>
+      <c r="EF15" t="inlineStr">
+        <is>
+          <t>D2 antipsychotic</t>
+        </is>
       </c>
       <c r="EG15" t="inlineStr">
         <is>
-          <t>D2 antipsychotic</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH15" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL15" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK15" t="inlineStr">
         <is>
           <t>NCT04512066 (2020) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM15">
+      <c r="EL15">
         <v>1</v>
       </c>
     </row>
@@ -5146,69 +5131,69 @@
           <t>34</t>
         </is>
       </c>
+      <c r="DB16">
+        <v>16</v>
+      </c>
       <c r="DC16">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="DD16">
+        <v>0</v>
+      </c>
+      <c r="DE16">
         <v>34</v>
       </c>
-      <c r="DE16">
+      <c r="DF16">
         <v>0</v>
       </c>
-      <c r="DF16">
+      <c r="DG16">
         <v>34</v>
       </c>
-      <c r="DG16">
+      <c r="DH16">
+        <v>2</v>
+      </c>
+      <c r="DI16">
+        <v>34</v>
+      </c>
+      <c r="DJ16">
+        <v>7</v>
+      </c>
+      <c r="DK16">
+        <v>34</v>
+      </c>
+      <c r="DL16">
         <v>0</v>
       </c>
-      <c r="DH16">
+      <c r="DM16">
         <v>34</v>
       </c>
-      <c r="DI16">
-        <v>2</v>
-      </c>
-      <c r="DJ16">
+      <c r="DN16">
+        <v>5</v>
+      </c>
+      <c r="DO16">
         <v>34</v>
       </c>
-      <c r="DK16">
-        <v>7</v>
-      </c>
-      <c r="DL16">
-        <v>34</v>
-      </c>
-      <c r="DM16">
-        <v>0</v>
-      </c>
-      <c r="DN16">
-        <v>34</v>
-      </c>
-      <c r="DO16">
-        <v>5</v>
-      </c>
-      <c r="DP16">
-        <v>34</v>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
       </c>
       <c r="EG16" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH16" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL16" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK16" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM16">
+      <c r="EL16">
         <v>1</v>
       </c>
     </row>
@@ -5318,69 +5303,69 @@
           <t>35</t>
         </is>
       </c>
+      <c r="DB17">
+        <v>34</v>
+      </c>
       <c r="DC17">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="DD17">
+        <v>5</v>
+      </c>
+      <c r="DE17">
         <v>35</v>
       </c>
-      <c r="DE17">
-        <v>5</v>
-      </c>
       <c r="DF17">
+        <v>0</v>
+      </c>
+      <c r="DG17">
         <v>35</v>
       </c>
-      <c r="DG17">
-        <v>0</v>
-      </c>
       <c r="DH17">
+        <v>10</v>
+      </c>
+      <c r="DI17">
         <v>35</v>
       </c>
-      <c r="DI17">
-        <v>10</v>
-      </c>
       <c r="DJ17">
+        <v>4</v>
+      </c>
+      <c r="DK17">
         <v>35</v>
       </c>
-      <c r="DK17">
-        <v>4</v>
-      </c>
       <c r="DL17">
+        <v>12</v>
+      </c>
+      <c r="DM17">
         <v>35</v>
       </c>
-      <c r="DM17">
-        <v>12</v>
-      </c>
       <c r="DN17">
+        <v>21</v>
+      </c>
+      <c r="DO17">
         <v>35</v>
       </c>
-      <c r="DO17">
-        <v>21</v>
-      </c>
-      <c r="DP17">
-        <v>35</v>
+      <c r="EF17" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL17" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM17">
+      <c r="EL17">
         <v>1</v>
       </c>
     </row>
@@ -5490,69 +5475,69 @@
           <t>36</t>
         </is>
       </c>
+      <c r="DB18">
+        <v>15</v>
+      </c>
       <c r="DC18">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="DD18">
+        <v>0</v>
+      </c>
+      <c r="DE18">
         <v>36</v>
       </c>
-      <c r="DE18">
+      <c r="DF18">
+        <v>3</v>
+      </c>
+      <c r="DG18">
+        <v>36</v>
+      </c>
+      <c r="DH18">
+        <v>1</v>
+      </c>
+      <c r="DI18">
+        <v>36</v>
+      </c>
+      <c r="DJ18">
+        <v>1</v>
+      </c>
+      <c r="DK18">
+        <v>36</v>
+      </c>
+      <c r="DL18">
         <v>0</v>
       </c>
-      <c r="DF18">
+      <c r="DM18">
         <v>36</v>
       </c>
-      <c r="DG18">
-        <v>3</v>
-      </c>
-      <c r="DH18">
+      <c r="DN18">
+        <v>5</v>
+      </c>
+      <c r="DO18">
         <v>36</v>
       </c>
-      <c r="DI18">
-        <v>1</v>
-      </c>
-      <c r="DJ18">
-        <v>36</v>
-      </c>
-      <c r="DK18">
-        <v>1</v>
-      </c>
-      <c r="DL18">
-        <v>36</v>
-      </c>
-      <c r="DM18">
-        <v>0</v>
-      </c>
-      <c r="DN18">
-        <v>36</v>
-      </c>
-      <c r="DO18">
-        <v>5</v>
-      </c>
-      <c r="DP18">
-        <v>36</v>
+      <c r="EF18" t="inlineStr">
+        <is>
+          <t>D2 antipsychotic</t>
+        </is>
       </c>
       <c r="EG18" t="inlineStr">
         <is>
-          <t>D2 antipsychotic</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH18" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL18" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK18" t="inlineStr">
         <is>
           <t>Perini (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM18">
+      <c r="EL18">
         <v>1</v>
       </c>
     </row>
@@ -5657,63 +5642,63 @@
           <t>63</t>
         </is>
       </c>
+      <c r="DB19">
+        <v>2</v>
+      </c>
       <c r="DC19">
-        <v>2</v>
-      </c>
-      <c r="DD19">
         <v>63</v>
       </c>
+      <c r="DH19">
+        <v>1</v>
+      </c>
       <c r="DI19">
+        <v>63</v>
+      </c>
+      <c r="DL19">
         <v>1</v>
       </c>
-      <c r="DJ19">
+      <c r="DM19">
         <v>63</v>
       </c>
-      <c r="DM19">
+      <c r="DN19">
+        <v>0</v>
+      </c>
+      <c r="DO19">
+        <v>63</v>
+      </c>
+      <c r="DR19">
         <v>1</v>
       </c>
-      <c r="DN19">
-        <v>63</v>
-      </c>
-      <c r="DO19">
-        <v>0</v>
-      </c>
-      <c r="DP19">
-        <v>63</v>
-      </c>
       <c r="DS19">
-        <v>1</v>
-      </c>
-      <c r="DT19">
         <v>59</v>
       </c>
+      <c r="EF19" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
       <c r="EG19" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH19" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EI19">
+        <v>1.248958333333333</v>
       </c>
       <c r="EJ19">
-        <v>1.248958333333333</v>
-      </c>
-      <c r="EK19">
         <v>2.100625000000001</v>
       </c>
-      <c r="EL19" t="inlineStr">
+      <c r="EK19" t="inlineStr">
         <is>
           <t>Tsukada (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM19">
+      <c r="EL19">
         <v>2</v>
       </c>
     </row>
@@ -5828,63 +5813,63 @@
           <t>63</t>
         </is>
       </c>
+      <c r="DB20">
+        <v>32</v>
+      </c>
       <c r="DC20">
-        <v>32</v>
-      </c>
-      <c r="DD20">
         <v>63</v>
       </c>
+      <c r="DH20">
+        <v>7</v>
+      </c>
       <c r="DI20">
-        <v>7</v>
-      </c>
-      <c r="DJ20">
         <v>63</v>
       </c>
+      <c r="DL20">
+        <v>16</v>
+      </c>
       <c r="DM20">
+        <v>63</v>
+      </c>
+      <c r="DN20">
         <v>16</v>
       </c>
-      <c r="DN20">
+      <c r="DO20">
         <v>63</v>
       </c>
-      <c r="DO20">
-        <v>16</v>
-      </c>
-      <c r="DP20">
-        <v>63</v>
+      <c r="DR20">
+        <v>5</v>
       </c>
       <c r="DS20">
-        <v>5</v>
-      </c>
-      <c r="DT20">
         <v>62</v>
       </c>
+      <c r="EF20" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
+      </c>
       <c r="EG20" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH20" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EI20">
+        <v>1.248958333333333</v>
       </c>
       <c r="EJ20">
-        <v>1.248958333333333</v>
-      </c>
-      <c r="EK20">
         <v>2.100625000000001</v>
       </c>
-      <c r="EL20" t="inlineStr">
+      <c r="EK20" t="inlineStr">
         <is>
           <t>Tsukada (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM20">
+      <c r="EL20">
         <v>2</v>
       </c>
     </row>
@@ -5994,57 +5979,57 @@
           <t>12</t>
         </is>
       </c>
+      <c r="DB21">
+        <v>1</v>
+      </c>
       <c r="DC21">
+        <v>12</v>
+      </c>
+      <c r="DL21">
         <v>1</v>
       </c>
-      <c r="DD21">
+      <c r="DM21">
         <v>12</v>
       </c>
-      <c r="DM21">
-        <v>1</v>
-      </c>
       <c r="DN21">
+        <v>0</v>
+      </c>
+      <c r="DO21">
         <v>12</v>
       </c>
-      <c r="DO21">
+      <c r="DP21">
         <v>0</v>
       </c>
-      <c r="DP21">
+      <c r="DQ21">
         <v>12</v>
       </c>
-      <c r="DQ21">
+      <c r="DR21">
         <v>0</v>
       </c>
-      <c r="DR21">
+      <c r="DS21">
         <v>12</v>
       </c>
-      <c r="DS21">
-        <v>0</v>
-      </c>
-      <c r="DT21">
-        <v>12</v>
+      <c r="EF21" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG21" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH21" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL21" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK21" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EM21">
+      <c r="EL21">
         <v>2</v>
       </c>
     </row>
@@ -6154,57 +6139,57 @@
           <t>12</t>
         </is>
       </c>
+      <c r="DB22">
+        <v>1</v>
+      </c>
       <c r="DC22">
+        <v>12</v>
+      </c>
+      <c r="DL22">
+        <v>0</v>
+      </c>
+      <c r="DM22">
+        <v>12</v>
+      </c>
+      <c r="DN22">
         <v>1</v>
       </c>
-      <c r="DD22">
+      <c r="DO22">
         <v>12</v>
       </c>
-      <c r="DM22">
+      <c r="DP22">
         <v>0</v>
       </c>
-      <c r="DN22">
+      <c r="DQ22">
         <v>12</v>
       </c>
-      <c r="DO22">
-        <v>1</v>
-      </c>
-      <c r="DP22">
+      <c r="DR22">
+        <v>0</v>
+      </c>
+      <c r="DS22">
         <v>12</v>
       </c>
-      <c r="DQ22">
-        <v>0</v>
-      </c>
-      <c r="DR22">
-        <v>12</v>
-      </c>
-      <c r="DS22">
-        <v>0</v>
-      </c>
-      <c r="DT22">
-        <v>12</v>
+      <c r="EF22" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG22" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH22" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL22" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK22" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EM22">
+      <c r="EL22">
         <v>2</v>
       </c>
     </row>
@@ -6314,57 +6299,57 @@
           <t>24</t>
         </is>
       </c>
+      <c r="DB23">
+        <v>1</v>
+      </c>
       <c r="DC23">
-        <v>1</v>
-      </c>
-      <c r="DD23">
         <v>24</v>
       </c>
+      <c r="DL23">
+        <v>0</v>
+      </c>
       <c r="DM23">
+        <v>24</v>
+      </c>
+      <c r="DN23">
         <v>0</v>
       </c>
-      <c r="DN23">
+      <c r="DO23">
         <v>24</v>
       </c>
-      <c r="DO23">
+      <c r="DP23">
         <v>0</v>
       </c>
-      <c r="DP23">
+      <c r="DQ23">
         <v>24</v>
       </c>
-      <c r="DQ23">
+      <c r="DR23">
         <v>0</v>
       </c>
-      <c r="DR23">
+      <c r="DS23">
         <v>24</v>
       </c>
-      <c r="DS23">
-        <v>0</v>
-      </c>
-      <c r="DT23">
-        <v>24</v>
+      <c r="EF23" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
       </c>
       <c r="EG23" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH23" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL23" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK23" t="inlineStr">
         <is>
           <t>Hopkins (2021) - ulotaront</t>
         </is>
       </c>
-      <c r="EM23">
+      <c r="EL23">
         <v>2</v>
       </c>
     </row>
@@ -6454,33 +6439,33 @@
           <t>16</t>
         </is>
       </c>
+      <c r="DB24">
+        <v>6</v>
+      </c>
       <c r="DC24">
-        <v>6</v>
-      </c>
-      <c r="DD24">
         <v>15</v>
       </c>
+      <c r="EF24" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
+      </c>
       <c r="EG24" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH24" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL24" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK24" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM24">
+      <c r="EL24">
         <v>3</v>
       </c>
     </row>
@@ -6570,33 +6555,33 @@
           <t>16</t>
         </is>
       </c>
+      <c r="DB25">
+        <v>1</v>
+      </c>
       <c r="DC25">
-        <v>1</v>
-      </c>
-      <c r="DD25">
         <v>13</v>
       </c>
+      <c r="EF25" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
+      </c>
       <c r="EG25" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH25" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL25" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK25" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM25">
+      <c r="EL25">
         <v>3</v>
       </c>
     </row>
@@ -6686,33 +6671,33 @@
           <t>16</t>
         </is>
       </c>
+      <c r="DB26">
+        <v>2</v>
+      </c>
       <c r="DC26">
-        <v>2</v>
-      </c>
-      <c r="DD26">
         <v>14</v>
       </c>
+      <c r="EF26" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
       <c r="EG26" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH26" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL26" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK26" t="inlineStr">
         <is>
           <t>Szabo (2023) - ulotaront</t>
         </is>
       </c>
-      <c r="EM26">
+      <c r="EL26">
         <v>3</v>
       </c>
     </row>
@@ -6864,62 +6849,57 @@
           <t>no</t>
         </is>
       </c>
-      <c r="CS27" t="inlineStr">
-        <is>
-          <t>52 weeks</t>
-        </is>
+      <c r="DD27">
+        <v>7</v>
       </c>
       <c r="DE27">
-        <v>7</v>
+        <v>201</v>
       </c>
       <c r="DF27">
+        <v>28</v>
+      </c>
+      <c r="DG27">
         <v>201</v>
       </c>
-      <c r="DG27">
-        <v>28</v>
-      </c>
-      <c r="DH27">
+      <c r="DN27">
+        <v>12</v>
+      </c>
+      <c r="DO27">
         <v>201</v>
       </c>
-      <c r="DO27">
-        <v>12</v>
-      </c>
-      <c r="DP27">
+      <c r="DX27">
+        <v>30</v>
+      </c>
+      <c r="DY27">
         <v>201</v>
       </c>
-      <c r="DY27">
-        <v>30</v>
-      </c>
-      <c r="DZ27">
+      <c r="ED27">
+        <v>8</v>
+      </c>
+      <c r="EE27">
         <v>201</v>
       </c>
-      <c r="EE27">
-        <v>8</v>
-      </c>
-      <c r="EF27">
-        <v>201</v>
+      <c r="EF27" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG27" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>&gt;13 weeks</t>
         </is>
       </c>
       <c r="EH27" t="inlineStr">
         <is>
-          <t>&gt;13 weeks</t>
-        </is>
-      </c>
-      <c r="EI27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL27" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK27" t="inlineStr">
         <is>
           <t>NCT04115319 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EM27">
+      <c r="EL27">
         <v>1</v>
       </c>
     </row>
@@ -7071,62 +7051,57 @@
           <t>no</t>
         </is>
       </c>
-      <c r="CS28" t="inlineStr">
-        <is>
-          <t>52 weeks</t>
-        </is>
+      <c r="DD28">
+        <v>12</v>
       </c>
       <c r="DE28">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="DF28">
+        <v>10</v>
+      </c>
+      <c r="DG28">
         <v>102</v>
       </c>
-      <c r="DG28">
-        <v>10</v>
-      </c>
-      <c r="DH28">
+      <c r="DN28">
+        <v>21</v>
+      </c>
+      <c r="DO28">
         <v>102</v>
       </c>
-      <c r="DO28">
-        <v>21</v>
-      </c>
-      <c r="DP28">
+      <c r="DX28">
+        <v>11</v>
+      </c>
+      <c r="DY28">
         <v>102</v>
       </c>
-      <c r="DY28">
+      <c r="ED28">
         <v>11</v>
       </c>
-      <c r="DZ28">
+      <c r="EE28">
         <v>102</v>
       </c>
-      <c r="EE28">
-        <v>11</v>
-      </c>
-      <c r="EF28">
-        <v>102</v>
+      <c r="EF28" t="inlineStr">
+        <is>
+          <t>D2 antipsychotic</t>
+        </is>
       </c>
       <c r="EG28" t="inlineStr">
         <is>
-          <t>D2 antipsychotic</t>
+          <t>&gt;13 weeks</t>
         </is>
       </c>
       <c r="EH28" t="inlineStr">
         <is>
-          <t>&gt;13 weeks</t>
-        </is>
-      </c>
-      <c r="EI28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL28" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK28" t="inlineStr">
         <is>
           <t>NCT04115319 (2019) - ulotaront</t>
         </is>
       </c>
-      <c r="EM28">
+      <c r="EL28">
         <v>1</v>
       </c>
     </row>
@@ -7387,69 +7362,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB29">
+        <v>4</v>
+      </c>
       <c r="DC29">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="DD29">
+        <v>1</v>
+      </c>
+      <c r="DE29">
         <v>12</v>
       </c>
-      <c r="DE29">
-        <v>1</v>
-      </c>
-      <c r="DF29">
+      <c r="DH29">
+        <v>0</v>
+      </c>
+      <c r="DI29">
         <v>12</v>
       </c>
-      <c r="DI29">
+      <c r="DJ29">
         <v>0</v>
       </c>
-      <c r="DJ29">
+      <c r="DK29">
         <v>12</v>
       </c>
-      <c r="DK29">
+      <c r="DL29">
+        <v>2</v>
+      </c>
+      <c r="DM29">
+        <v>12</v>
+      </c>
+      <c r="DN29">
         <v>0</v>
       </c>
-      <c r="DL29">
+      <c r="DO29">
         <v>12</v>
       </c>
-      <c r="DM29">
+      <c r="DX29">
         <v>2</v>
       </c>
-      <c r="DN29">
+      <c r="DY29">
         <v>12</v>
       </c>
-      <c r="DO29">
-        <v>0</v>
-      </c>
-      <c r="DP29">
-        <v>12</v>
-      </c>
-      <c r="DY29">
-        <v>2</v>
-      </c>
-      <c r="DZ29">
-        <v>12</v>
+      <c r="EF29" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG29" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH29" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL29" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK29" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM29">
+      <c r="EL29">
         <v>1</v>
       </c>
     </row>
@@ -7710,69 +7685,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB30">
+        <v>7</v>
+      </c>
       <c r="DC30">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="DD30">
+        <v>0</v>
+      </c>
+      <c r="DE30">
         <v>15</v>
       </c>
-      <c r="DE30">
+      <c r="DH30">
         <v>0</v>
       </c>
-      <c r="DF30">
+      <c r="DI30">
         <v>15</v>
       </c>
-      <c r="DI30">
+      <c r="DJ30">
         <v>0</v>
       </c>
-      <c r="DJ30">
+      <c r="DK30">
         <v>15</v>
       </c>
-      <c r="DK30">
+      <c r="DL30">
         <v>0</v>
       </c>
-      <c r="DL30">
+      <c r="DM30">
         <v>15</v>
       </c>
-      <c r="DM30">
+      <c r="DN30">
         <v>0</v>
       </c>
-      <c r="DN30">
+      <c r="DO30">
         <v>15</v>
       </c>
-      <c r="DO30">
-        <v>0</v>
-      </c>
-      <c r="DP30">
+      <c r="DX30">
+        <v>1</v>
+      </c>
+      <c r="DY30">
         <v>15</v>
       </c>
-      <c r="DY30">
-        <v>1</v>
-      </c>
-      <c r="DZ30">
-        <v>15</v>
+      <c r="EF30" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
       </c>
       <c r="EG30" t="inlineStr">
         <is>
-          <t>placebo</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH30" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL30" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK30" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM30">
+      <c r="EL30">
         <v>1</v>
       </c>
     </row>
@@ -8033,69 +8008,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB31">
+        <v>2</v>
+      </c>
       <c r="DC31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="DD31">
+        <v>0</v>
+      </c>
+      <c r="DE31">
         <v>5</v>
       </c>
-      <c r="DE31">
+      <c r="DH31">
+        <v>1</v>
+      </c>
+      <c r="DI31">
+        <v>5</v>
+      </c>
+      <c r="DJ31">
         <v>0</v>
       </c>
-      <c r="DF31">
+      <c r="DK31">
         <v>5</v>
       </c>
-      <c r="DI31">
-        <v>1</v>
-      </c>
-      <c r="DJ31">
+      <c r="DL31">
+        <v>0</v>
+      </c>
+      <c r="DM31">
         <v>5</v>
       </c>
-      <c r="DK31">
+      <c r="DN31">
         <v>0</v>
       </c>
-      <c r="DL31">
+      <c r="DO31">
         <v>5</v>
       </c>
-      <c r="DM31">
+      <c r="DX31">
         <v>0</v>
       </c>
-      <c r="DN31">
+      <c r="DY31">
         <v>5</v>
       </c>
-      <c r="DO31">
-        <v>0</v>
-      </c>
-      <c r="DP31">
-        <v>5</v>
-      </c>
-      <c r="DY31">
-        <v>0</v>
-      </c>
-      <c r="DZ31">
-        <v>5</v>
+      <c r="EF31" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist (add-on)</t>
+        </is>
       </c>
       <c r="EG31" t="inlineStr">
         <is>
-          <t>TAAR1 agonist (add-on)</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH31" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL31" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK31" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM31">
+      <c r="EL31">
         <v>1</v>
       </c>
     </row>
@@ -8356,69 +8331,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB32">
+        <v>8</v>
+      </c>
       <c r="DC32">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="DD32">
+        <v>1</v>
+      </c>
+      <c r="DE32">
         <v>30</v>
       </c>
-      <c r="DE32">
+      <c r="DH32">
+        <v>2</v>
+      </c>
+      <c r="DI32">
+        <v>30</v>
+      </c>
+      <c r="DJ32">
         <v>1</v>
       </c>
-      <c r="DF32">
+      <c r="DK32">
         <v>30</v>
       </c>
-      <c r="DI32">
+      <c r="DL32">
+        <v>1</v>
+      </c>
+      <c r="DM32">
+        <v>30</v>
+      </c>
+      <c r="DN32">
         <v>2</v>
       </c>
-      <c r="DJ32">
+      <c r="DO32">
         <v>30</v>
       </c>
-      <c r="DK32">
-        <v>1</v>
-      </c>
-      <c r="DL32">
+      <c r="DX32">
+        <v>0</v>
+      </c>
+      <c r="DY32">
         <v>30</v>
       </c>
-      <c r="DM32">
-        <v>1</v>
-      </c>
-      <c r="DN32">
-        <v>30</v>
-      </c>
-      <c r="DO32">
-        <v>2</v>
-      </c>
-      <c r="DP32">
-        <v>30</v>
-      </c>
-      <c r="DY32">
-        <v>0</v>
-      </c>
-      <c r="DZ32">
-        <v>30</v>
+      <c r="EF32" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist (add-on)</t>
+        </is>
       </c>
       <c r="EG32" t="inlineStr">
         <is>
-          <t>TAAR1 agonist (add-on)</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH32" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL32" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK32" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM32">
+      <c r="EL32">
         <v>1</v>
       </c>
     </row>
@@ -8679,69 +8654,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB33">
+        <v>4</v>
+      </c>
       <c r="DC33">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="DD33">
+        <v>0</v>
+      </c>
+      <c r="DE33">
         <v>32</v>
       </c>
-      <c r="DE33">
+      <c r="DH33">
+        <v>1</v>
+      </c>
+      <c r="DI33">
+        <v>32</v>
+      </c>
+      <c r="DJ33">
         <v>0</v>
       </c>
-      <c r="DF33">
+      <c r="DK33">
         <v>32</v>
       </c>
-      <c r="DI33">
+      <c r="DL33">
         <v>1</v>
       </c>
-      <c r="DJ33">
+      <c r="DM33">
         <v>32</v>
       </c>
-      <c r="DK33">
+      <c r="DN33">
         <v>0</v>
       </c>
-      <c r="DL33">
+      <c r="DO33">
         <v>32</v>
       </c>
-      <c r="DM33">
-        <v>1</v>
-      </c>
-      <c r="DN33">
+      <c r="DX33">
+        <v>0</v>
+      </c>
+      <c r="DY33">
         <v>32</v>
       </c>
-      <c r="DO33">
-        <v>0</v>
-      </c>
-      <c r="DP33">
-        <v>32</v>
-      </c>
-      <c r="DY33">
-        <v>0</v>
-      </c>
-      <c r="DZ33">
-        <v>32</v>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist (add-on)</t>
+        </is>
       </c>
       <c r="EG33" t="inlineStr">
         <is>
-          <t>TAAR1 agonist (add-on)</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH33" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL33" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK33" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM33">
+      <c r="EL33">
         <v>1</v>
       </c>
     </row>
@@ -9002,69 +8977,69 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="DB34">
+        <v>9</v>
+      </c>
       <c r="DC34">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="DD34">
+        <v>0</v>
+      </c>
+      <c r="DE34">
         <v>37</v>
       </c>
-      <c r="DE34">
+      <c r="DH34">
+        <v>1</v>
+      </c>
+      <c r="DI34">
+        <v>37</v>
+      </c>
+      <c r="DJ34">
+        <v>3</v>
+      </c>
+      <c r="DK34">
+        <v>37</v>
+      </c>
+      <c r="DL34">
+        <v>2</v>
+      </c>
+      <c r="DM34">
+        <v>37</v>
+      </c>
+      <c r="DN34">
+        <v>2</v>
+      </c>
+      <c r="DO34">
+        <v>37</v>
+      </c>
+      <c r="DX34">
         <v>0</v>
       </c>
-      <c r="DF34">
+      <c r="DY34">
         <v>37</v>
       </c>
-      <c r="DI34">
-        <v>1</v>
-      </c>
-      <c r="DJ34">
-        <v>37</v>
-      </c>
-      <c r="DK34">
-        <v>3</v>
-      </c>
-      <c r="DL34">
-        <v>37</v>
-      </c>
-      <c r="DM34">
-        <v>2</v>
-      </c>
-      <c r="DN34">
-        <v>37</v>
-      </c>
-      <c r="DO34">
-        <v>2</v>
-      </c>
-      <c r="DP34">
-        <v>37</v>
-      </c>
-      <c r="DY34">
-        <v>0</v>
-      </c>
-      <c r="DZ34">
-        <v>37</v>
+      <c r="EF34" t="inlineStr">
+        <is>
+          <t>placebo (add-on)</t>
+        </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>placebo (add-on)</t>
+          <t>3-13 weeks</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>3-13 weeks</t>
-        </is>
-      </c>
-      <c r="EI34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL34" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr">
         <is>
           <t>NCT03669640 (2018) - ralmitaront</t>
         </is>
       </c>
-      <c r="EM34">
+      <c r="EL34">
         <v>1</v>
       </c>
     </row>
@@ -9159,57 +9134,57 @@
           <t>29</t>
         </is>
       </c>
+      <c r="DB35">
+        <v>20</v>
+      </c>
       <c r="DC35">
-        <v>20</v>
-      </c>
-      <c r="DD35">
         <v>29</v>
       </c>
+      <c r="DH35">
+        <v>4</v>
+      </c>
       <c r="DI35">
+        <v>29</v>
+      </c>
+      <c r="DL35">
+        <v>8</v>
+      </c>
+      <c r="DM35">
+        <v>29</v>
+      </c>
+      <c r="DN35">
         <v>4</v>
       </c>
-      <c r="DJ35">
+      <c r="DO35">
         <v>29</v>
       </c>
-      <c r="DM35">
-        <v>8</v>
-      </c>
-      <c r="DN35">
+      <c r="DR35">
+        <v>0</v>
+      </c>
+      <c r="DS35">
         <v>29</v>
       </c>
-      <c r="DO35">
-        <v>4</v>
-      </c>
-      <c r="DP35">
-        <v>29</v>
-      </c>
-      <c r="DS35">
-        <v>0</v>
-      </c>
-      <c r="DT35">
-        <v>29</v>
+      <c r="EF35" t="inlineStr">
+        <is>
+          <t>TAAR1 agonist</t>
+        </is>
       </c>
       <c r="EG35" t="inlineStr">
         <is>
-          <t>TAAR1 agonist</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH35" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL35" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK35" t="inlineStr">
         <is>
           <t>NCT05402111 (2022) - ulotaront</t>
         </is>
       </c>
-      <c r="EM35">
+      <c r="EL35">
         <v>1</v>
       </c>
     </row>
@@ -9299,57 +9274,57 @@
           <t>26</t>
         </is>
       </c>
+      <c r="DB36">
+        <v>9</v>
+      </c>
       <c r="DC36">
-        <v>9</v>
-      </c>
-      <c r="DD36">
         <v>26</v>
       </c>
+      <c r="DH36">
+        <v>0</v>
+      </c>
       <c r="DI36">
+        <v>26</v>
+      </c>
+      <c r="DL36">
         <v>0</v>
       </c>
-      <c r="DJ36">
+      <c r="DM36">
         <v>26</v>
       </c>
-      <c r="DM36">
+      <c r="DN36">
+        <v>1</v>
+      </c>
+      <c r="DO36">
+        <v>26</v>
+      </c>
+      <c r="DR36">
         <v>0</v>
       </c>
-      <c r="DN36">
+      <c r="DS36">
         <v>26</v>
       </c>
-      <c r="DO36">
-        <v>1</v>
-      </c>
-      <c r="DP36">
-        <v>26</v>
-      </c>
-      <c r="DS36">
-        <v>0</v>
-      </c>
-      <c r="DT36">
-        <v>26</v>
+      <c r="EF36" t="inlineStr">
+        <is>
+          <t>D2 antipsychotic</t>
+        </is>
       </c>
       <c r="EG36" t="inlineStr">
         <is>
-          <t>D2 antipsychotic</t>
+          <t>1 day-2 weeks</t>
         </is>
       </c>
       <c r="EH36" t="inlineStr">
         <is>
-          <t>1 day-2 weeks</t>
-        </is>
-      </c>
-      <c r="EI36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="EL36" t="inlineStr">
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="EK36" t="inlineStr">
         <is>
           <t>NCT05402111 (2022) - ulotaront</t>
         </is>
       </c>
-      <c r="EM36">
+      <c r="EL36">
         <v>1</v>
       </c>
     </row>
